--- a/Анализ_изменений_Приложение_2_ПП_2464.xlsx
+++ b/Анализ_изменений_Приложение_2_ПП_2464.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Полные тексты рядом" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Пофразовый анализ'!$A$1:$F$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Пофразовый анализ'!$A$1:$F$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,17 +540,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="50" customHeight="1">
+    <row r="1" ht="55" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Пофразовый анализ изменений Приложения № 2 к Правилам обучения по охране труда и проверки знания требований охраны труда (Постановление Правительства РФ от 24.12.2021 № 2464)</t>
+          <t>Пофразовый анализ изменений Приложения № 2 к Правилам обучения по охране труда и проверки знания требований охраны труда (Постановление Правительства РФ от 24.12.2021 № 2464). Все формулировки приведены ПОЛНОСТЬЮ, без сокращений.</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Исходная редакция Приложения № 2 (без отметки об изменении N 805) ↔ Редакция с изменениями N 805 от 30.06.2026</t>
+          <t>Исходная редакция Приложения № 2 ↔ Редакция с изменениями N 805 от 30.06.2026</t>
         </is>
       </c>
     </row>
@@ -578,15 +578,15 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Источник</t>
+          <t>Принцип таблицы</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ГАРАНТ (экспорт PDF от 04.08.2026)</t>
+          <t>В колонках «Было» и «Стало» — полные дословные формулировки из текстов редакций. Знак «—» означает отсутствие соответствующей фразы.</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Из теоретического курса исключены: понятие «первая помощь», детализация прав/обязанностей/ответственности, виды кровотечений (А/В/К/смешанное), перечень способов остановки с перечислением техник, носовое кровотечение, травматический шок, особенности реанимации у детей, ошибки/осложнения реанимации, детализация травм по областям тела в прежней формулировке, химические/электрические поражения и излучение как отдельная строка в старой новой редакции появились иначе.</t>
+          <t>Из теоретического курса исключены, в частности: понятие «первая помощь»; детализация прав/обязанностей/ответственности; классификация видов кровотечений; носовое кровотечение; травматический шок; ошибки и прекращение реанимации; особенности реанимации у детей; детальный разбор травм по областям тела.</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Добавлены: приоритетность оказания первой помощи; извлечение из труднодоступных мест (в теорию темы 1); использование АНД (автоматический наружный дефибриллятор); «иные угрожающие жизни нарушения дыхания»; укусы/ужаливания; судорожный приступ; помощь в принятии лекарств; транспортировка; опрос пострадавшего; поражения химическими/электрическими факторами и излучением (в теме 4 новой редакции).</t>
+          <t>Добавлены, в частности: приоритетность оказания первой помощи; извлечение из труднодоступных мест (теория темы 1); использование АНД; иные угрожающие жизни нарушения дыхания; укусы и ужаливания; судорожный приступ; помощь в принятии лекарств; транспортировка; опрос пострадавшего; поражения химическими и электрическими факторами, излучением.</t>
         </is>
       </c>
     </row>
@@ -648,64 +648,54 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Практические занятия существенно перегруппированы: практика по кровотечениям расширена (давящая повязка, жгуты, инородный предмет); в реанимации добавлены АНД и последовательность реанимационных мероприятий; из практики кровотечений/травм убраны детальные перечни артерий и способов; часть приёмов перенесена в тему 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="55" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Легенда окраски в листах «Пофразовый анализ» и др.: зелёный — добавлено; красный — исключено; жёлтый — переформулирование/переработка; голубой — перенос/структура; серый — без существенных изменений.</t>
+          <t>Практические занятия перегруппированы: в блоке кровотечений убраны пальцевое прижатие артерий и максимальное сгибание конечности; добавлены спина и смежные зоны; в реанимации добавлен АНД и изменён порядок «компрессии → искусственное дыхание».</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Легенда окраски</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Легенда</t>
+      <c r="A14" s="7" t="inlineStr"/>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr"/>
+      <c r="A15" s="9" t="inlineStr"/>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Добавлено</t>
+          <t>Исключено</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr"/>
+      <c r="A16" s="10" t="inlineStr"/>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Исключено</t>
+          <t>Переформулирование / переработка / сокращение / расширение</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr"/>
+      <c r="A17" s="11" t="inlineStr"/>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Переформулирование / переработка</t>
+          <t>Перенесено / структурное изменение</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr"/>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Перенесено / структурное изменение</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Без существенных изменений</t>
+          <t>Без изменений</t>
         </is>
       </c>
     </row>
@@ -727,9 +717,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -741,12 +731,12 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Было (исходная редакция)</t>
+          <t>Было (исходная редакция) — полная формулировка</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Стало (ред. N 805 от 30.06.2026)</t>
+          <t>Стало (ред. N 805 от 30.06.2026) — полная формулировка</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
@@ -760,7 +750,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="70" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
           <t>1</t>
@@ -778,16 +768,16 @@
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>Без изменений (по смыслу)</t>
+          <t>Без изменений</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>Название темы сохранено</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
+          <t>Название темы сохранено дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="70" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
           <t>2</t>
@@ -810,11 +800,11 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>Содержание прежней темы 2 перенесено в новую тему 3; в тему 2 выделено содержание о кровотечениях (из прежней темы 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
+          <t>Содержание прежней темы 2 перенесено в новую тему 3; в тему 2 выделено содержание о кровотечениях (из прежней темы 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>3</t>
@@ -837,11 +827,11 @@
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>Прежняя тема 3 разделена: кровотечения → новая тема 2; травмы → новая тема 4; номер 3 занят блоком реанимации</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>Прежняя тема 3 разделена: кровотечения → новая тема 2; травмы → новая тема 4; номер 3 занят блоком реанимации.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
           <t>4</t>
@@ -864,7 +854,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>В тему 4 включены травмы/ранения (из прежней темы 3) и прочие состояния (прежняя тема 4); название расширено</t>
+          <t>В тему 4 включены травмы и ранения (из прежней темы 3) и прочие состояния (прежняя тема 4); название расширено.</t>
         </is>
       </c>
     </row>
@@ -879,15 +869,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -898,12 +888,12 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Было (исходная редакция)</t>
+          <t>Было (исходная редакция) — полная формулировка</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Стало (ред. N 805 от 30.06.2026)</t>
+          <t>Стало (ред. N 805 от 30.06.2026) — полная формулировка</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
@@ -918,11 +908,11 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Детальный комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
           <t>ТЕМА 1. Организационно-правовые аспекты оказания первой помощи</t>
@@ -946,7 +936,7 @@
       <c r="E3" s="18" t="n"/>
       <c r="F3" s="18" t="n"/>
     </row>
-    <row r="4" ht="54" customHeight="1">
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -978,7 +968,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="67" customHeight="1">
+    <row r="5" ht="96" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
           <t>1.2</t>
@@ -986,7 +976,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Понятие «первая помощь». Перечень состояний, при которых оказывается первая помощь, перечень мероприятий по ее оказанию.</t>
+          <t>Понятие "первая помощь". Перечень состояний, при которых оказывается первая помощь, перечень мероприятий по ее оказанию.</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
@@ -1007,11 +997,11 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>Исключено понятие «первая помощь». Добавлены «порядок» и «приоритетность» оказания первой помощи. Перечень состояний/мероприятий вынесен в отдельный абзац; добавлена «последовательность их выполнения».</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="66" customHeight="1">
+          <t>Исключено понятие "первая помощь". Добавлены «порядок» и «приоритетность» оказания первой помощи. Перечень состояний и мероприятий вынесен в отдельный абзац; добавлена «последовательность их выполнения».</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
           <t>1.3</t>
@@ -1039,11 +1029,11 @@
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>Убраны примеры конкретных аптечек (автомобильная, для работников). Введена обобщённая терминология: «укладки, наборы, комплекты и аптечки». Фраза «Основные компоненты и их назначение» сохранена по смыслу.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="110" customHeight="1">
+          <t>Убраны примеры конкретных аптечек (автомобильная, для работников). Введена обобщённая терминология: «укладки, наборы, комплекты и аптечки».</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="112" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
           <t>1.4</t>
@@ -1071,7 +1061,7 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>Исключены: «общая последовательность действий на месте происшествия», «правила личной безопасности», уточнение про факторы риска и их устранение, детализация путей передачи инфекций (контакт, кровь, биожидкости). Оставлена краткая формула про безопасность и профилактику инфекций. Часть смысла о последовательности действий покрыта новой фразой про «порядок» и «приоритетность» (п. 1.2).</t>
+          <t>Исключены общая последовательность действий на месте происшествия, правила личной безопасности, уточнение про факторы риска и их устранение, детализация путей передачи инфекций. Часть смысла о последовательности действий покрыта новой фразой про «порядок» и «приоритетность» (п. 1.2).</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1073,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>— (отсутствовало в теме 1)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -1103,11 +1093,11 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>Новый теоретический пункт темы 1. Ранее близкие навыки отрабатывались только практически в теме 4 (экстренное извлечение / перемещение).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
+          <t>Новый теоретический пункт темы 1. Ранее близкие навыки отрабатывались только практически в теме 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
           <t>1.6</t>
@@ -1135,14 +1125,14 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>Минорная правка: убрано слово «Основные»; союз «и других» заменён на «других» (перечисление через запятую). Смысл сохранён.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
+          <t>Убрано слово «Основные»; союз «и других» заменён на перечисление через запятую («других»). Смысл сохранён.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>ПЕРЕСТРОЙКА ТЕМ 2–4 (сводка соответствия)</t>
+          <t>ПЕРЕСТРОЙКА ТЕМ 2–4 (соответствие блоков)</t>
         </is>
       </c>
       <c r="B10" s="16" t="n"/>
@@ -1151,7 +1141,7 @@
       <c r="E10" s="16" t="n"/>
       <c r="F10" s="16" t="n"/>
     </row>
-    <row r="11" ht="40" customHeight="1">
+    <row r="11" ht="48" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
           <t>С.1</t>
@@ -1159,12 +1149,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Тема 2 (сознание / дыхание / кровообращение) → теория + практика</t>
+          <t>Тема 2. Оказание первой помощи при отсутствии сознания, остановке дыхания и кровообращения</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Тема 3 (сознание / дыхание / кровообращение) → теория + практика</t>
+          <t>Тема 3. Оказание первой помощи при отсутствии сознания, остановке дыхания и кровообращения</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -1179,11 +1169,11 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Блок реанимации сдвинут с номера 2 на номер 3 и существенно переработан по содержанию.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
+          <t>Блок реанимации сдвинут с номера 2 на номер 3 и переработан по содержанию.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
           <t>С.2</t>
@@ -1191,12 +1181,13 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Тема 3 (наружные кровотечения и травмы) → теория + практика</t>
+          <t>Тема 3. Оказание первой помощи при наружных кровотечениях и травмах</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Тема 2 (только наружные кровотечения) + часть темы 4 (травмы, ранения)</t>
+          <t>Тема 2. Оказание первой помощи при наружных кровотечениях
+(травмы — в теме 4)</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -1215,7 +1206,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="40" customHeight="1">
+    <row r="13" ht="48" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
           <t>С.3</t>
@@ -1223,12 +1214,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Тема 4 (прочие состояния) → теория + практика</t>
+          <t>Тема 4. Оказание первой помощи при прочих состояниях</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Тема 4 (травмы, ранения, поражения и прочие состояния)</t>
+          <t>Тема 4. Оказание первой помощи при травмах, ранениях, поражениях и прочих состояниях</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -1243,14 +1234,14 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>«Прочие состояния» сохранены внутри темы 4, но тема расширена за счёт травм/ранений/поражений.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
+          <t>«Прочие состояния» сохранены внутри темы 4, тема расширена за счёт травм, ранений и поражений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>ТЕМА 2 (НОВАЯ). Оказание первой помощи при наружных кровотечениях  ←  было в Теме 3</t>
+          <t>ТЕМА 2 (НОВАЯ). Оказание первой помощи при наружных кровотечениях  ←  содержание из Темы 3 (исходной)</t>
         </is>
       </c>
       <c r="B14" s="16" t="n"/>
@@ -1271,7 +1262,7 @@
       <c r="E15" s="18" t="n"/>
       <c r="F15" s="18" t="n"/>
     </row>
-    <row r="16" ht="50" customHeight="1">
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -1299,11 +1290,11 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>Убраны «цель и порядок выполнения». Добавлено слово «Кровотечение» как заход. Введено указание на осмотр нескольких пострадавших: «(пострадавших)».</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="59" customHeight="1">
+          <t>Убраны «цель и порядок выполнения». Добавлено слово «Кровотечение». Введено указание на осмотр нескольких пострадавших: «(пострадавших)».</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="128" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
         <is>
           <t>2.2</t>
@@ -1311,12 +1302,13 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Понятия «кровотечение», «острая кровопотеря». Признаки различных видов наружного кровотечения (артериального, венозного, капиллярного, смешанного).</t>
+          <t>Понятия "кровотечение", "острая кровопотеря". Признаки различных видов наружного кровотечения (артериального, венозного, капиллярного, смешанного). Способы временной остановки наружного кровотечения: пальцевое прижатие артерии, наложение жгута, максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
         </is>
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>Признаки наружного кровотечения и кровопотери.</t>
+          <t>Признаки наружного кровотечения и кровопотери.
+Способы временной остановки наружного кровотечения.</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -1331,43 +1323,43 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>Исключены отдельные понятия «кровотечение»/«острая кровопотеря» как термины и классификация видов кровотечения (артериальное, венозное, капиллярное, смешанное). Формулировка обобщена.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="62" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+          <t>Исключены отдельные понятия «кровотечение»/«острая кровопотеря» и классификация видов кровотечения. Перечень конкретных способов остановки убран из теории; оставлена общая формулировка. Часть способов сохранена в практике темы 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>Способы временной остановки наружного кровотечения: пальцевое прижатие артерии, наложение жгута, максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>Способы временной остановки наружного кровотечения.</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>Тема 2 / теория ← Тема 3 / теория</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>Сокращение / обобщение</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>Перечень конкретных способов (пальцевое прижатие, жгут, сгибание, прямое давление, давящая повязка) убран из теории; оставлена общая формулировка. Часть способов сохранена в практике темы 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1">
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Последовательность выполнения мероприятий по остановке кровотечения.</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>Тема 2 / теория</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>Новый акцент на последовательности действий при остановке кровотечения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
         <is>
           <t>2.4</t>
@@ -1375,12 +1367,12 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>— (отсутствовало как отдельная фраза)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>Последовательность выполнения мероприятий по остановке кровотечения.</t>
+          <t>Остановка кровотечения при ранениях различных областей тела.</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -1395,43 +1387,43 @@
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Новый акцент на последовательности действий при остановке кровотечения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
+          <t>В теорию внесён отдельный пункт про остановку кровотечения при ранениях разных областей тела.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>— (отсутствовало как отдельная фраза; частично покрывалось практикой и разбором травм по областям)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>Остановка кровотечения при ранениях различных областей тела.</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>Тема 2 / теория</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>Добавлено</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>В теорию внесён отдельный пункт про остановку кровотечения при ранениях разных областей тела.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="40" customHeight="1">
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Оказание первой помощи при носовом кровотечении.</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>Тема 3 (исходная) / теория</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>Отдельный пункт о носовом кровотечении удалён из перечня тем.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
       <c r="A21" s="21" t="inlineStr">
         <is>
           <t>2.6</t>
@@ -1439,17 +1431,17 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>Оказание первой помощи при носовом кровотечении.</t>
+          <t>Понятие о травматическом шоке, причины и признаки. Мероприятия, предупреждающие развитие травматического шока.</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>— (исключено)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>Тема 2 / теория ← Тема 3 / теория</t>
+          <t>Тема 3 (исходная) / теория</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -1459,55 +1451,55 @@
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>Отдельный пункт о носовом кровотечении удалён из перечня тем.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="41" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
+          <t>Тема травматического шока отсутствует в новой редакции Приложения № 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Практическое занятие по теме 2 (новая) ← часть практики темы 3 (исходной)</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>Понятие о травматическом шоке, причины и признаки. Мероприятия, предупреждающие развитие травматического шока.</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>— (исключено из блока кровотечений; в новой теме 4 напрямую не воспроизведено)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>Тема 3 (стар.) / теория</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>Исключено</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>Тема травматического шока отсутствует в новой редакции Приложения № 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>Практическое занятие по теме 2 (новая) ← часть практики темы 3 (старой)</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="n"/>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>Отработка проведения обзорного осмотра пострадавшего.</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>Отработка проведения обзорного осмотра пострадавшего (пострадавших).</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>Тема 2 / практика ← Тема 3 / практика</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Переформулирование</t>
+        </is>
+      </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>Добавлено указание на осмотр нескольких пострадавших.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="192" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
           <t>2.8</t>
@@ -1515,48 +1507,48 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>Отработка проведения обзорного осмотра пострадавшего.</t>
+          <t>Отработка приемов временной остановки наружного кровотечения при ранениях головы, шеи, груди, живота, таза и конечностей с помощью пальцевого прижатия артерий (сонной, подключичной, подмышечной, плечевой, бедренной); наложение табельного и импровизированного кровоостанавливающего жгута (жгута-закрутки, ремня), максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
         </is>
       </c>
       <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>Отработка проведения обзорного осмотра пострадавшего (пострадавших).</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>Тема 2 / практика ← Тема 3 / практика</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>Добавлено указание на осмотр нескольких пострадавших.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="115" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>Отработка приемов временной остановки наружного кровотечения при ранениях головы, шеи, груди, живота, таза и конечностей с помощью пальцевого прижатия артерий (сонной, подключичной, подмышечной, плечевой, бедренной); наложение табельного и импровизированного кровоостанавливающего жгута (жгута-закрутки, ремня), максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>Отработка временной остановки наружного кровотечения при ранении головы, шеи, груди, спины, живота, конечностей и смежных зон с помощью прямого давления на рану.
 Отработка наложения давящей повязки при ранении головы, груди, спины, живота, конечностей и смежных зон.
 Отработка приемов наложения табельных и импровизированных кровоостанавливающих жгутов разных конструкций при ранении конечностей.</t>
         </is>
       </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>Тема 2 / практика ← Тема 3 / практика</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Существенная переработка</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>Убраны: пальцевое прижатие конкретных артерий, максимальное сгибание конечности в суставе, уточнения «жгут-закрутка, ремень», ранения таза. Добавлены: «спина», «смежные зоны», «жгуты разных конструкций». Прямое давление, давящая повязка и жгуты разведены по отдельным практическим пунктам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок при наличии инородного предмета в ране живота, груди, конечностей.</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения давящей повязки с фиксацией инородного предмета в ране живота, груди, спины, конечностей.</t>
+        </is>
+      </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Тема 2 / практика ← Тема 3 / практика</t>
@@ -1564,487 +1556,487 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>Существенная переработка</t>
+          <t>Переформулирование</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>1) Убраны: пальцевое прижатие конкретных артерий, максимальное сгибание конечности в суставе, уточнения «жгут-закрутка/ремень», ранения таза. 2) Добавлены: «спина», «смежные зоны», «жгуты разных конструкций». 3) Прямое давление, давящая повязка и жгуты разведены по отдельным практическим пунктам.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="43" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+          <t>Уточнён тип повязки — «давящая повязка с фиксацией инородного предмета»; добавлена область «спина».</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="192" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения повязок при наличии инородного предмета в ране живота, груди, конечностей.</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения давящей повязки с фиксацией инородного предмета в ране живота, груди, спины, конечностей.</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>Тема 2 / практика ← Тема 3 / практика</t>
-        </is>
-      </c>
-      <c r="E26" s="19" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Проведение подробного осмотра пострадавшего.
+Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.
+Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий).
+Отработка приемов фиксации шейного отдела позвоночника.</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>— (в теме 2 не сохранено; см. практику темы 4 — полные формулировки в п. 4.13–4.17)</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Тема 2 / практика</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Перенесено</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Практические пункты по подробному осмотру, окклюзионной повязке, переломам и фиксации шеи исключены из блока кровотечений и сохранены/перенесены в практику новой темы 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>ТЕМА 3 (НОВАЯ). Оказание первой помощи при отсутствии сознания, остановке дыхания и кровообращения  ←  была Тема 2</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="16" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Теоретическое занятие</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Основные признаки жизни у пострадавшего. Причины нарушения дыхания и кровообращения. Способы проверки сознания, дыхания, кровообращения у пострадавшего.</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>Определение признаков жизни.</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>Тема 3 / теория ← Тема 2 / теория</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Сокращение / обобщение</t>
+        </is>
+      </c>
+      <c r="F29" s="19" t="inlineStr">
+        <is>
+          <t>Убраны «причины нарушения дыхания и кровообращения» и детализация «способы проверки сознания, дыхания, кровообращения». Оставлено общее «определение признаков жизни».</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>Восстановление и поддержание проходимости дыхательных путей.</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>Тема 3 / теория</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>Отдельный теоретический пункт о проходимости дыхательных путей.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>Современный алгоритм проведения сердечно-легочной реанимации (далее - реанимация). Техника проведения искусственного дыхания и давления руками на грудину пострадавшего при проведении реанимации.</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>Техника проведения сердечно-легочной реанимации.</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>Тема 3 / теория ← Тема 2 / теория</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>Сокращение / обобщение</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>Убраны слова «современный алгоритм», сокращение «далее - реанимация» и детализация техники искусственного дыхания и давления на грудину в теории.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>Использование автоматического наружного дефибриллятора (при его наличии).</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>Тема 3 / теория</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>Новый элемент: автоматический наружный дефибриллятор (АНД) в теоретической программе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Ошибки и осложнения, возникающие при выполнении реанимационных мероприятий. Показания к прекращению реанимации. Мероприятия, выполняемые после прекращения реанимации.</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>Тема 2 (исходная) / теория</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>Блок об ошибках, осложнениях, показаниях к прекращению реанимации и действиях после прекращения удалён.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>Особенности реанимации у детей.</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>Тема 2 (исходная) / теория</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>Отдельный пункт об особенностях реанимации у детей удалён.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="80" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Порядок оказания первой помощи при частичном и полном нарушении проходимости верхних дыхательных путей, вызванном инородным телом у пострадавших в сознании, без сознания. Особенности оказания первой помощи тучному пострадавшему, беременной женщине и ребенку.</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>Первая помощь при нарушении проходимости верхних дыхательных путей, вызванном инородным телом.</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>Тема 3 / теория ← Тема 2 / теория</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>Сокращение / обобщение</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>Убраны различия частичного и полного нарушения, состояния сознания и без сознания, особенности для тучного пострадавшего, беременной женщины и ребенка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>Первая помощь при иных угрожающих жизни и здоровью нарушениях дыхания.</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>Тема 3 / теория</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>Новый общий пункт о прочих угрожающих нарушениях дыхания (сверх инородного тела).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>Практическое занятие по теме 3 (новая) ← практика темы 2 (исходной)</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>Выполнение алгоритма реанимации.</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>Отработка последовательности выполнения реанимационных мероприятий.</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>Тема 3 / практика ← Тема 2 / практика</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
         <is>
           <t>Переформулирование</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>Уточнён тип повязки — «давящая повязка с фиксацией инородного предмета»; добавлена область «спина».</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>Проведение подробного осмотра пострадавшего.
-Отработка наложения окклюзионной (герметизирующей) повязки…
-Отработка приемов первой помощи при переломах…
-Отработка приемов фиксации шейного отдела позвоночника.</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>— (в теме 2 не осталось; перенесено в тему 4)</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Тема 2 / практика</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Перенесено</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>Практические пункты по подробному осмотру, окклюзионной повязке, переломам и фиксации шеи исключены из блока кровотечений и перенесены/сохранены в практике новой темы 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>ТЕМА 3 (НОВАЯ). Оказание первой помощи при отсутствии сознания, остановке дыхания и кровообращения  ←  была Тема 2</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Теоретическое занятие</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="n"/>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="18" t="n"/>
-    </row>
-    <row r="30" ht="55" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>Основные признаки жизни у пострадавшего. Причины нарушения дыхания и кровообращения. Способы проверки сознания, дыхания, кровообращения у пострадавшего.</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>Определение признаков жизни.</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>Тема 3 / теория ← Тема 2 / теория</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>Сокращение / обобщение</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>Убраны «причины нарушения дыхания и кровообращения» и детализация «способы проверки сознания, дыхания, кровообращения». Оставлено общее «определение признаков жизни».</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="45" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>— (отсутствовало как отдельная фраза)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>Восстановление и поддержание проходимости дыхательных путей.</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="inlineStr">
-        <is>
-          <t>Тема 3 / теория</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="inlineStr">
-        <is>
-          <t>Добавлено</t>
-        </is>
-      </c>
-      <c r="F31" s="20" t="inlineStr">
-        <is>
-          <t>Отдельный теоретический пункт о проходимости дыхательных путей (ранее близкий смысл был в практике и в блоке инородного тела).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="62" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>Современный алгоритм проведения сердечно-легочной реанимации (далее — реанимация). Техника проведения искусственного дыхания и давления руками на грудину пострадавшего при проведении реанимации.</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>Техника проведения сердечно-легочной реанимации.</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>Тема 3 / теория ← Тема 2 / теория</t>
-        </is>
-      </c>
-      <c r="E32" s="19" t="inlineStr">
-        <is>
-          <t>Сокращение / обобщение</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>Убраны слова «современный алгоритм», сокращение «далее — реанимация» и детализация техники ИВЛ/компрессий в теории. Формулировка сжата до «техника проведения СЛР».</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="40" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>— (отсутствовало)</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>Использование автоматического наружного дефибриллятора (при его наличии).</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>Тема 3 / теория</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="inlineStr">
-        <is>
-          <t>Добавлено</t>
-        </is>
-      </c>
-      <c r="F33" s="20" t="inlineStr">
-        <is>
-          <t>Новый элемент: АНД в теоретической программе.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="55" customHeight="1">
-      <c r="A34" s="21" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>Ошибки и осложнения, возникающие при выполнении реанимационных мероприятий. Показания к прекращению реанимации. Мероприятия, выполняемые после прекращения реанимации.</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>— (исключено)</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>Тема 3 / теория ← Тема 2 / теория</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>Исключено</t>
-        </is>
-      </c>
-      <c r="F34" s="21" t="inlineStr">
-        <is>
-          <t>Блок об ошибках, осложнениях, показаниях к прекращению реанимации и действиях после прекращения удалён.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="40" customHeight="1">
-      <c r="A35" s="21" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="inlineStr">
-        <is>
-          <t>Особенности реанимации у детей.</t>
-        </is>
-      </c>
-      <c r="C35" s="21" t="inlineStr">
-        <is>
-          <t>— (исключено)</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="inlineStr">
-        <is>
-          <t>Тема 3 / теория ← Тема 2 / теория</t>
-        </is>
-      </c>
-      <c r="E35" s="21" t="inlineStr">
-        <is>
-          <t>Исключено</t>
-        </is>
-      </c>
-      <c r="F35" s="21" t="inlineStr">
-        <is>
-          <t>Отдельный пункт об особенностях реанимации у детей удалён.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="78" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="inlineStr">
-        <is>
-          <t>Порядок оказания первой помощи при частичном и полном нарушении проходимости верхних дыхательных путей, вызванном инородным телом у пострадавших в сознании, без сознания. Особенности оказания первой помощи тучному пострадавшему, беременной женщине и ребенку.</t>
-        </is>
-      </c>
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>Первая помощь при нарушении проходимости верхних дыхательных путей, вызванном инородным телом.</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>Тема 3 / теория ← Тема 2 / теория</t>
-        </is>
-      </c>
-      <c r="E36" s="19" t="inlineStr">
-        <is>
-          <t>Сокращение / обобщение</t>
-        </is>
-      </c>
-      <c r="F36" s="19" t="inlineStr">
-        <is>
-          <t>Убраны различия частичного/полного нарушения, состояния сознания/без сознания, особенности для тучного, беременной и ребёнка. Формулировка обобщена.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="40" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="inlineStr">
-        <is>
-          <t>— (отсутствовало)</t>
-        </is>
-      </c>
-      <c r="C37" s="20" t="inlineStr">
-        <is>
-          <t>Первая помощь при иных угрожающих жизни и здоровью нарушениях дыхания.</t>
-        </is>
-      </c>
-      <c r="D37" s="20" t="inlineStr">
-        <is>
-          <t>Тема 3 / теория</t>
-        </is>
-      </c>
-      <c r="E37" s="20" t="inlineStr">
-        <is>
-          <t>Добавлено</t>
-        </is>
-      </c>
-      <c r="F37" s="20" t="inlineStr">
-        <is>
-          <t>Новый общий пункт о прочих угрожающих нарушениях дыхания (сверх инородного тела).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>Практическое занятие по теме 3 (новая) ← практика темы 2 (старой)</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="n"/>
-      <c r="C38" s="18" t="n"/>
-      <c r="D38" s="18" t="n"/>
-      <c r="E38" s="18" t="n"/>
-      <c r="F38" s="18" t="n"/>
-    </row>
-    <row r="39" ht="50" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>3.9</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>— (отсутствовало как отдельный пункт; был «Выполнение алгоритма реанимации»)</t>
-        </is>
-      </c>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>Отработка последовательности выполнения реанимационных мероприятий.</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>Тема 3 / практика</t>
-        </is>
-      </c>
-      <c r="E39" s="19" t="inlineStr">
+      <c r="F38" s="19" t="inlineStr">
+        <is>
+          <t>Формулировка заменена и вынесена в начало практики.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Оценка обстановки на месте происшествия.</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Оценка обстановки на месте происшествия.</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Тема 3 / практика ← Тема 2 / практика</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>Отработка навыков определения сознания у пострадавшего.</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>Отработка приемов определения сознания у пострадавшего.</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>Тема 3 / практика ← Тема 2 / практика</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
         <is>
           <t>Переформулирование</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
-        <is>
-          <t>«Выполнение алгоритма реанимации» заменено на «отработку последовательности выполнения реанимационных мероприятий» и вынесено в начало практики.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="40" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>Оценка обстановки на месте происшествия.</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>Оценка обстановки на месте происшествия.</t>
-        </is>
-      </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>Тема 3 / практика ← Тема 2 / практика</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>Без изменений (по смыслу)</t>
-        </is>
-      </c>
-      <c r="F40" s="13" t="inlineStr">
-        <is>
-          <t>Формулировка сохранена дословно.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="40" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>3.11</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t>Отработка навыков определения сознания у пострадавшего.</t>
-        </is>
-      </c>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t>Отработка приемов определения сознания у пострадавшего.</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t>Тема 3 / практика ← Тема 2 / практика</t>
-        </is>
-      </c>
-      <c r="E41" s="19" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-      <c r="F41" s="19" t="inlineStr">
-        <is>
-          <t>«навыков» → «приемов».</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
+        <is>
+          <t>Слово «навыков» заменено на «приемов».</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>Отработка приемов восстановления проходимости верхних дыхательных путей. Оценка признаков жизни у пострадавшего.</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>Отработка приемов восстановления проходимости верхних дыхательных путей.
 Оценка признаков жизни у пострадавшего.</t>
         </is>
       </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>Тема 3 / практика ← Тема 2 / практика</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>Содержание сохранено; в новой редакции оформлено двумя отдельными абзацами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>Отработка вызова скорой медицинской помощи, других специальных служб.</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Отработка вызова скорой медицинской помощи, других специальных служб.</t>
+        </is>
+      </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
           <t>Тема 3 / практика ← Тема 2 / практика</t>
@@ -2052,127 +2044,127 @@
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>Без изменений (по смыслу)</t>
+          <t>Без изменений</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>Содержание сохранено; в новой редакции оформлено двумя отдельными абзацами.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="40" customHeight="1">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>Отработка вызова скорой медицинской помощи, других специальных служб.</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="inlineStr">
-        <is>
-          <t>Отработка вызова скорой медицинской помощи, других специальных служб.</t>
-        </is>
-      </c>
-      <c r="D43" s="13" t="inlineStr">
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="112" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>Отработка приемов искусственного дыхания "рот ко рту", "рот к носу" с применением устройств для искусственного дыхания.
+Отработка приемов давления руками на грудину пострадавшего.</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>Отработка приемов давления руками на грудину пострадавшего.
+Отработка приемов искусственного дыхания "рот ко рту", "рот к носу" с применением устройств для искусственного дыхания.</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
         <is>
           <t>Тема 3 / практика ← Тема 2 / практика</t>
         </is>
       </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>Без изменений (по смыслу)</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="inlineStr">
-        <is>
-          <t>Дословно сохранено.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="58" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="B44" s="19" t="inlineStr">
-        <is>
-          <t>Отработка приемов искусственного дыхания «рот ко рту», «рот к носу» с применением устройств для искусственного дыхания.
-Отработка приемов давления руками на грудину пострадавшего.</t>
-        </is>
-      </c>
-      <c r="C44" s="19" t="inlineStr">
-        <is>
-          <t>Отработка приемов давления руками на грудину пострадавшего.
-Отработка приемов искусственного дыхания «рот ко рту», «рот к носу» с применением устройств для искусственного дыхания.</t>
-        </is>
-      </c>
-      <c r="D44" s="19" t="inlineStr">
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>Переформулирование</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>Содержание то же; изменён порядок: сначала давление на грудину, затем искусственное дыхание.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="48" customHeight="1">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>Отработка приема перевода пострадавшего в устойчивое боковое положение.</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>Отработка приема перевода пострадавшего в устойчивое боковое положение.</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>Тема 3 / практика ← Тема 2 / практика</t>
         </is>
       </c>
-      <c r="E44" s="19" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-      <c r="F44" s="19" t="inlineStr">
-        <is>
-          <t>Содержание то же; изменён порядок: сначала компрессии, затем искусственное дыхание (соответствует современной последовательности СЛР).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="40" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="B45" s="19" t="inlineStr">
-        <is>
-          <t>Выполнение алгоритма реанимации.</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="inlineStr">
-        <is>
-          <t>— (см. п. 3.9: заменено формулировкой о последовательности реанимационных мероприятий)</t>
-        </is>
-      </c>
-      <c r="D45" s="19" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>Отработка алгоритма применения автоматического наружного дефибриллятора.</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
         <is>
           <t>Тема 3 / практика</t>
         </is>
       </c>
-      <c r="E45" s="19" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-      <c r="F45" s="19" t="inlineStr">
-        <is>
-          <t>Пункт как отдельная строка с прежней формулировкой не сохранён.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="40" customHeight="1">
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>Новый практический навык — применение автоматического наружного дефибриллятора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="48" customHeight="1">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>Отработка приема перевода пострадавшего в устойчивое боковое положение.</t>
+          <t>Отработка приемов удаления инородного тела из верхних дыхательных путей пострадавшего.</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>Отработка приема перевода пострадавшего в устойчивое боковое положение.</t>
+          <t>Отработка приемов удаления инородного тела из верхних дыхательных путей пострадавшего.</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
@@ -2182,267 +2174,266 @@
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>Без изменений (по смыслу)</t>
+          <t>Без изменений</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>Дословно сохранено.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="40" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="inlineStr">
-        <is>
-          <t>— (отсутствовало)</t>
-        </is>
-      </c>
-      <c r="C47" s="20" t="inlineStr">
-        <is>
-          <t>Отработка алгоритма применения автоматического наружного дефибриллятора.</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="inlineStr">
-        <is>
-          <t>Тема 3 / практика</t>
-        </is>
-      </c>
-      <c r="E47" s="20" t="inlineStr">
-        <is>
-          <t>Добавлено</t>
-        </is>
-      </c>
-      <c r="F47" s="20" t="inlineStr">
-        <is>
-          <t>Новый практический навык — применение АНД.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="40" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>Отработка приемов удаления инородного тела из верхних дыхательных путей пострадавшего.</t>
-        </is>
-      </c>
-      <c r="C48" s="13" t="inlineStr">
-        <is>
-          <t>Отработка приемов удаления инородного тела из верхних дыхательных путей пострадавшего.</t>
-        </is>
-      </c>
-      <c r="D48" s="13" t="inlineStr">
-        <is>
-          <t>Тема 3 / практика ← Тема 2 / практика</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>Без изменений (по смыслу)</t>
-        </is>
-      </c>
-      <c r="F48" s="13" t="inlineStr">
-        <is>
-          <t>Дословно сохранено.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="15" t="inlineStr">
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>ТЕМА 4 (НОВАЯ). Оказание первой помощи при травмах, ранениях, поражениях и прочих состояниях  ←  Тема 3 (травмы) + Тема 4 (прочие)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>Теоретическое занятие — блок травм / осмотра (из старой темы 3)</t>
-        </is>
-      </c>
-      <c r="B50" s="18" t="n"/>
-      <c r="C50" s="18" t="n"/>
-      <c r="D50" s="18" t="n"/>
-      <c r="E50" s="18" t="n"/>
-      <c r="F50" s="18" t="n"/>
-    </row>
-    <row r="51" ht="49" customHeight="1">
-      <c r="A51" s="19" t="inlineStr">
+      <c r="B47" s="16" t="n"/>
+      <c r="C47" s="16" t="n"/>
+      <c r="D47" s="16" t="n"/>
+      <c r="E47" s="16" t="n"/>
+      <c r="F47" s="16" t="n"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>Теоретическое занятие — блок травм и осмотра (из исходной темы 3)</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="n"/>
+      <c r="C48" s="18" t="n"/>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+    </row>
+    <row r="49" ht="64" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>Цель и последовательность подробного осмотра пострадавшего. Основные состояния, с которыми может столкнуться участник оказания первой помощи.</t>
         </is>
       </c>
-      <c r="C51" s="19" t="inlineStr">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>Подробный осмотр и опрос пострадавшего.
 Основные состояния, с которыми может столкнуться участник оказания первой помощи.</t>
         </is>
       </c>
-      <c r="D51" s="19" t="inlineStr">
+      <c r="D49" s="19" t="inlineStr">
         <is>
           <t>Тема 4 / теория ← Тема 3 / теория</t>
         </is>
       </c>
-      <c r="E51" s="19" t="inlineStr">
+      <c r="E49" s="19" t="inlineStr">
         <is>
           <t>Переформулирование</t>
         </is>
       </c>
-      <c r="F51" s="19" t="inlineStr">
-        <is>
-          <t>Убраны «цель и последовательность». Добавлен «опрос» пострадавшего. Фраза про основные состояния сохранена.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="72" customHeight="1">
+      <c r="F49" s="19" t="inlineStr">
+        <is>
+          <t>Убраны «цель и последовательность». Добавлен «опрос» пострадавшего. Фраза про основные состояния сохранена дословно отдельным абзацем.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="220" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>Травмы головы. Оказание первой помощи. Особенности ранений волосистой части головы. Особенности оказания первой помощи при травмах глаза и носа.
+Травмы шеи, оказание первой помощи. Временная остановка наружного кровотечения при травмах шеи. Фиксация шейного отдела позвоночника (вручную, подручными средствами, с использованием медицинских изделий).
+Травмы груди, оказание первой помощи. Основные проявления травмы груди, особенности наложения повязок при травме груди, наложение окклюзионной (герметизирующей) повязки. Особенности наложения повязки на рану груди с инородным телом.
+Травмы живота и таза, основные проявления. Оказание первой помощи.
+Закрытая травма живота с признаками внутреннего кровотечения. Оказание первой помощи. Особенности наложения повязок на рану при выпадении органов брюшной полости, при наличии инородного тела в ране.
+Травмы конечностей, оказание первой помощи. Понятие "иммобилизация". Способы иммобилизации при травме конечностей.
+Травмы позвоночника. Оказание первой помощи.</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>Травмы различных областей тела.</t>
+        </is>
+      </c>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>Тема 4 / теория ← Тема 3 / теория</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>Сокращение / обобщение</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="inlineStr">
+        <is>
+          <t>Детальный разбор травм по областям тела с особенностями помощи свёрнут в одну общую фразу. Часть практических навыков сохранена в практике темы 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>Теоретическое занятие — поражения и прочие состояния (из исходной темы 4 + новые позиции)</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+    </row>
+    <row r="52" ht="176" customHeight="1">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>Травмы головы. Оказание первой помощи. Особенности ранений волосистой части головы. Особенности оказания первой помощи при травмах глаза и носа.
-Травмы шеи…
-Травмы груди…
-Травмы живота и таза…
-Травмы конечностей…
-Травмы позвоночника…</t>
-        </is>
-      </c>
-      <c r="C52" s="19" t="inlineStr">
-        <is>
-          <t>Травмы различных областей тела.</t>
-        </is>
-      </c>
-      <c r="D52" s="19" t="inlineStr">
-        <is>
-          <t>Тема 4 / теория ← Тема 3 / теория</t>
-        </is>
-      </c>
-      <c r="E52" s="19" t="inlineStr">
-        <is>
-          <t>Сокращение / обобщение</t>
-        </is>
-      </c>
-      <c r="F52" s="19" t="inlineStr">
-        <is>
-          <t>Детальный разбор травм по областям (голова, шея, грудь, живот/таз, конечности, позвоночник) с особенностями помощи свёрнут в одну общую фразу.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="94" customHeight="1">
-      <c r="A53" s="21" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="B53" s="21" t="inlineStr">
-        <is>
-          <t>Фиксация шейного отдела позвоночника (вручную, подручными средствами, с использованием медицинских изделий) — в блоке травм шеи.
-Понятие «иммобилизация». Способы иммобилизации при травме конечностей. — в блоке травм конечностей.
-Наложение окклюзионной повязки, инородное тело в ране и т.п. — в блоках травм груди/живота.</t>
-        </is>
-      </c>
-      <c r="C53" s="21" t="inlineStr">
-        <is>
-          <t>— (как отдельные теоретические пункты исключены; частично сохранены в практике темы 4)</t>
-        </is>
-      </c>
-      <c r="D53" s="21" t="inlineStr">
-        <is>
-          <t>Тема 4 / теория</t>
-        </is>
-      </c>
-      <c r="E53" s="21" t="inlineStr">
-        <is>
-          <t>Исключено</t>
-        </is>
-      </c>
-      <c r="F53" s="21" t="inlineStr">
-        <is>
-          <t>Теоретическая детализация иммобилизации, фиксации шеи, окклюзионной повязки и особенностей по областям убрана из теории; соответствующие навыки остаются в практическом занятии темы 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="17" t="inlineStr">
-        <is>
-          <t>Теоретическое занятие — поражения и прочие состояния (из старой темы 4 + новые позиции)</t>
-        </is>
-      </c>
-      <c r="B54" s="18" t="n"/>
-      <c r="C54" s="18" t="n"/>
-      <c r="D54" s="18" t="n"/>
-      <c r="E54" s="18" t="n"/>
-      <c r="F54" s="18" t="n"/>
-    </row>
-    <row r="55" ht="102" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="B55" s="19" t="inlineStr">
         <is>
           <t>Виды ожогов, их признаки. Понятие о поверхностных и глубоких ожогах. Ожог верхних дыхательных путей, основные проявления. Оказание первой помощи.
 Перегревание, факторы, способствующие его развитию. Основные проявления, оказание первой помощи.
 Холодовая травма, ее виды. Основные проявления переохлаждения (гипотермии), отморожения, оказание первой помощи.</t>
         </is>
       </c>
-      <c r="C55" s="19" t="inlineStr">
-        <is>
-          <t>Поражения, вызванные термическими факторами, — ожоги, перегревание, отморожение, переохлаждение.</t>
-        </is>
-      </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>Поражения, вызванные термическими факторами, - ожоги, перегревание, отморожение, переохлаждение.</t>
+        </is>
+      </c>
+      <c r="D52" s="19" t="inlineStr">
         <is>
           <t>Тема 4 / теория ← Тема 4 / теория</t>
         </is>
       </c>
-      <c r="E55" s="19" t="inlineStr">
+      <c r="E52" s="19" t="inlineStr">
         <is>
           <t>Сокращение / обобщение</t>
         </is>
       </c>
-      <c r="F55" s="19" t="inlineStr">
-        <is>
-          <t>Детализация видов/признаков ожогов, ожога дыхательных путей, факторов перегревания, видов холодовой травмы и гипотермии свёрнута в одну обобщающую фразу о термических поражениях.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="40" customHeight="1">
+      <c r="F52" s="19" t="inlineStr">
+        <is>
+          <t>Детализация видов и признаков ожогов, ожога верхних дыхательных путей, факторов перегревания, видов холодовой травмы и гипотермии свёрнута в одну обобщающую фразу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="48" customHeight="1">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>Поражения, вызванные химическими и электрическими факторами, излучением.</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>Тема 4 / теория</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>Новый теоретический пункт: химические, электрические поражения и излучение.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>Отравления, пути попадания ядов в организм. Признаки острого отравления. Оказание первой помощи при попадании отравляющих веществ в организм через дыхательные пути, пищеварительный тракт, через кожу.</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>Отравления.</t>
+        </is>
+      </c>
+      <c r="D54" s="19" t="inlineStr">
+        <is>
+          <t>Тема 4 / теория ← Тема 4 / теория</t>
+        </is>
+      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>Сокращение / обобщение</t>
+        </is>
+      </c>
+      <c r="F54" s="19" t="inlineStr">
+        <is>
+          <t>Убраны пути попадания ядов, признаки острого отравления и детализация помощи по путям поступления.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C55" s="20" t="inlineStr">
+        <is>
+          <t>Укусы и ужаливания ядовитых животных.</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr">
+        <is>
+          <t>Тема 4 / теория</t>
+        </is>
+      </c>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>Новая тема теоретического курса.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="48" customHeight="1">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>— (в старой теме 4 не было отдельной строки; частично не покрывалось)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>Поражения, вызванные химическими и электрическими факторами, излучением.</t>
+          <t>Судорожный приступ с потерей сознания.</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
@@ -2457,262 +2448,262 @@
       </c>
       <c r="F56" s="20" t="inlineStr">
         <is>
-          <t>Новый теоретический пункт: химические, электрические поражения и излучение.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="63" customHeight="1">
-      <c r="A57" s="19" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="B57" s="19" t="inlineStr">
-        <is>
-          <t>Отравления, пути попадания ядов в организм. Признаки острого отравления. Оказание первой помощи при попадании отравляющих веществ в организм через дыхательные пути, пищеварительный тракт, через кожу.</t>
-        </is>
-      </c>
-      <c r="C57" s="19" t="inlineStr">
-        <is>
-          <t>Отравления.</t>
-        </is>
-      </c>
-      <c r="D57" s="19" t="inlineStr">
-        <is>
-          <t>Тема 4 / теория ← Тема 4 / теория</t>
-        </is>
-      </c>
-      <c r="E57" s="19" t="inlineStr">
-        <is>
-          <t>Сокращение / обобщение</t>
-        </is>
-      </c>
-      <c r="F57" s="19" t="inlineStr">
-        <is>
-          <t>Убраны пути попадания ядов, признаки острого отравления и детализация помощи по путям поступления.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="40" customHeight="1">
-      <c r="A58" s="20" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="B58" s="20" t="inlineStr">
-        <is>
-          <t>— (отсутствовало)</t>
-        </is>
-      </c>
-      <c r="C58" s="20" t="inlineStr">
-        <is>
-          <t>Укусы и ужаливания ядовитых животных.</t>
-        </is>
-      </c>
-      <c r="D58" s="20" t="inlineStr">
+          <t>Новая тема теоретического курса.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="48" customHeight="1">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C57" s="20" t="inlineStr">
+        <is>
+          <t>Помощь пострадавшему в принятии лекарственных препаратов.</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="inlineStr">
         <is>
           <t>Тема 4 / теория</t>
         </is>
       </c>
-      <c r="E58" s="20" t="inlineStr">
+      <c r="E57" s="20" t="inlineStr">
         <is>
           <t>Добавлено</t>
         </is>
       </c>
-      <c r="F58" s="20" t="inlineStr">
+      <c r="F57" s="20" t="inlineStr">
         <is>
           <t>Новая тема теоретического курса.</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="40" customHeight="1">
-      <c r="A59" s="20" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="B59" s="20" t="inlineStr">
-        <is>
-          <t>— (отсутствовало)</t>
-        </is>
-      </c>
-      <c r="C59" s="20" t="inlineStr">
-        <is>
-          <t>Судорожный приступ с потерей сознания.</t>
-        </is>
-      </c>
-      <c r="D59" s="20" t="inlineStr">
-        <is>
-          <t>Тема 4 / теория</t>
-        </is>
-      </c>
-      <c r="E59" s="20" t="inlineStr">
-        <is>
-          <t>Добавлено</t>
-        </is>
-      </c>
-      <c r="F59" s="20" t="inlineStr">
-        <is>
-          <t>Новая тема теоретического курса.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="40" customHeight="1">
-      <c r="A60" s="20" t="inlineStr">
+    <row r="58" ht="192" customHeight="1">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
       </c>
-      <c r="B60" s="20" t="inlineStr">
-        <is>
-          <t>— (отсутствовало)</t>
-        </is>
-      </c>
-      <c r="C60" s="20" t="inlineStr">
-        <is>
-          <t>Помощь пострадавшему в принятии лекарственных препаратов.</t>
-        </is>
-      </c>
-      <c r="D60" s="20" t="inlineStr">
-        <is>
-          <t>Тема 4 / теория</t>
-        </is>
-      </c>
-      <c r="E60" s="20" t="inlineStr">
-        <is>
-          <t>Добавлено</t>
-        </is>
-      </c>
-      <c r="F60" s="20" t="inlineStr">
-        <is>
-          <t>Новая тема теоретического курса.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="120" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="B61" s="19" t="inlineStr">
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t>Цель и принципы придания пострадавшим оптимальных положений тела. Оптимальные положения тела пострадавшего с травмами груди, живота, таза, конечностей, с потерей сознания, с признаками кровопотери.
 Способы контроля состояния пострадавшего, находящегося в сознании, без сознания.
 Психологическая поддержка. Цели оказания психологической поддержки. Общие принципы общения с пострадавшими, простые приемы их психологической поддержки.</t>
         </is>
       </c>
-      <c r="C61" s="19" t="inlineStr">
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>Придание и поддержание оптимального положения тела пострадавшего, контроль состояния, психологическая поддержка.</t>
         </is>
       </c>
-      <c r="D61" s="19" t="inlineStr">
+      <c r="D58" s="19" t="inlineStr">
         <is>
           <t>Тема 4 / теория ← Тема 4 / теория</t>
         </is>
       </c>
-      <c r="E61" s="19" t="inlineStr">
+      <c r="E58" s="19" t="inlineStr">
         <is>
           <t>Сокращение / обобщение</t>
         </is>
       </c>
-      <c r="F61" s="19" t="inlineStr">
-        <is>
-          <t>Три развёрнутых блока сжаты в одну комплексную фразу. Убраны цели/принципы, перечень оптимальных положений по видам травм, различия контроля при сознании/без сознания, цели и принципы психологической поддержки.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="40" customHeight="1">
-      <c r="A62" s="20" t="inlineStr">
+      <c r="F58" s="19" t="inlineStr">
+        <is>
+          <t>Три развёрнутых блока сжаты в одну комплексную фразу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="48" customHeight="1">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr">
+        <is>
+          <t>Транспортировка пострадавшего.</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>Тема 4 / теория</t>
+        </is>
+      </c>
+      <c r="E59" s="20" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
+        </is>
+      </c>
+      <c r="F59" s="20" t="inlineStr">
+        <is>
+          <t>Новый теоретический пункт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="48" customHeight="1">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>4.11</t>
         </is>
       </c>
-      <c r="B62" s="20" t="inlineStr">
-        <is>
-          <t>— (отсутствовало как отдельный пункт теории)</t>
-        </is>
-      </c>
-      <c r="C62" s="20" t="inlineStr">
-        <is>
-          <t>Транспортировка пострадавшего.</t>
-        </is>
-      </c>
-      <c r="D62" s="20" t="inlineStr">
-        <is>
-          <t>Тема 4 / теория</t>
-        </is>
-      </c>
-      <c r="E62" s="20" t="inlineStr">
-        <is>
-          <t>Добавлено</t>
-        </is>
-      </c>
-      <c r="F62" s="20" t="inlineStr">
-        <is>
-          <t>Новый теоретический пункт (ранее близкий смысл был в практике перемещения/переноски).</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="50" customHeight="1">
-      <c r="A63" s="19" t="inlineStr">
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>Принципы передачи пострадавшего бригаде скорой медицинской помощи, другим специальным службам, сотрудники которых обязаны оказывать первую помощь.</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="inlineStr">
+        <is>
+          <t>Передача пострадавшего выездной бригаде скорой медицинской помощи, медицинской организации, специальным службам.</t>
+        </is>
+      </c>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>Тема 4 / теория ← Тема 4 / теория</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>Переформулирование</t>
+        </is>
+      </c>
+      <c r="F60" s="19" t="inlineStr">
+        <is>
+          <t>Убрано слово «принципы»; добавлены «выездной» характер бригады и «медицинская организация»; убрана отсылка к обязанностям сотрудников специальных служб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>Практическое занятие по теме 4</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="n"/>
+      <c r="C61" s="18" t="n"/>
+      <c r="D61" s="18" t="n"/>
+      <c r="E61" s="18" t="n"/>
+      <c r="F61" s="18" t="n"/>
+    </row>
+    <row r="62" ht="48" customHeight="1">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>4.12</t>
         </is>
       </c>
-      <c r="B63" s="19" t="inlineStr">
-        <is>
-          <t>Принципы передачи пострадавшего бригаде скорой медицинской помощи, другим специальным службам, сотрудники которых обязаны оказывать первую помощь.</t>
-        </is>
-      </c>
-      <c r="C63" s="19" t="inlineStr">
-        <is>
-          <t>Передача пострадавшего выездной бригаде скорой медицинской помощи, медицинской организации, специальным службам.</t>
-        </is>
-      </c>
-      <c r="D63" s="19" t="inlineStr">
-        <is>
-          <t>Тема 4 / теория ← Тема 4 / теория</t>
-        </is>
-      </c>
-      <c r="E63" s="19" t="inlineStr">
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>Проведение подробного осмотра пострадавшего.</t>
+        </is>
+      </c>
+      <c r="C62" s="19" t="inlineStr">
+        <is>
+          <t>Проведение подробного осмотра и опроса пострадавшего.</t>
+        </is>
+      </c>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>Тема 4 / практика ← Тема 3 / практика</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
         <is>
           <t>Переформулирование</t>
         </is>
       </c>
-      <c r="F63" s="19" t="inlineStr">
-        <is>
-          <t>Убрано слово «принципы»; добавлены «выездной» характер бригады и «медицинская организация»; убрана отсылка к обязанностям сотрудников спецслужб.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="17" t="inlineStr">
-        <is>
-          <t>Практическое занятие по теме 4</t>
-        </is>
-      </c>
-      <c r="B64" s="18" t="n"/>
-      <c r="C64" s="18" t="n"/>
-      <c r="D64" s="18" t="n"/>
-      <c r="E64" s="18" t="n"/>
-      <c r="F64" s="18" t="n"/>
-    </row>
-    <row r="65" ht="40" customHeight="1">
+      <c r="F62" s="19" t="inlineStr">
+        <is>
+          <t>Добавлен опрос; пункт перенесён в практику темы 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>Тема 4 / практика ← Тема 3 / практика</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>Перенесено</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно; блок перемещён из практики исходной темы 3 в практику новой темы 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="48" customHeight="1">
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="B64" s="19" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок при наличии инородного предмета в ране живота, груди, конечностей.</t>
+        </is>
+      </c>
+      <c r="C64" s="19" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок на рану при выпадении органов брюшной полости, при наличии инородного предмета в ране живота, груди, спины, конечностей.</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>Тема 4 / практика ← Тема 3 / практика</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>Расширение / детализация</t>
+        </is>
+      </c>
+      <c r="F64" s="19" t="inlineStr">
+        <is>
+          <t>Добавлены выпадение органов брюшной полости и область «спина». Параллельно в теме 2 осталась давящая повязка с фиксацией инородного предмета.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="48" customHeight="1">
       <c r="A65" s="19" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t>Проведение подробного осмотра пострадавшего. (старая тема 3)</t>
+          <t>Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий).</t>
         </is>
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t>Проведение подробного осмотра и опроса пострадавшего.</t>
+          <t>Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий, обездвиживание руками травмированных частей тела).</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -2722,356 +2713,357 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
+          <t>Расширение / детализация</t>
+        </is>
+      </c>
+      <c r="F65" s="19" t="inlineStr">
+        <is>
+          <t>Добавлен способ: «обездвиживание руками травмированных частей тела».</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="48" customHeight="1">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>Отработка приемов фиксации шейного отдела позвоночника.</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>Отработка приемов фиксации шейного отдела позвоночника.</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>Тема 4 / практика ← Тема 3 / практика</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="inlineStr">
+        <is>
+          <t>Перенесено</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно; перенесено в тему 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="48" customHeight="1">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок при ожогах различных областей тела. Применение местного охлаждения.</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок при ожогах различных областей тела. Применение местного охлаждения.</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>Тема 4 / практика ← Тема 4 / практика</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="48" customHeight="1">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения термоизолирующей повязки при отморожениях.</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения термоизолирующей повязки при отморожениях.</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>Тема 4 / практика ← Тема 4 / практика</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="F68" s="13" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="48" customHeight="1">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>Отработка приемов придания оптимального положения тела пострадавшему при отсутствии сознания, травмах различных областей тела, значительной кровопотере.</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>Отработка приемов придания оптимального положения тела пострадавшему при отсутствии сознания, травмах различных областей тела, значительной кровопотере.</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>Тема 4 / практика ← Тема 4 / практика</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="48" customHeight="1">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>Отработка приемов экстренного извлечения пострадавшего из труднодоступного места, отработка основных приемов (пострадавший в сознании, пострадавший без сознания).</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>Отработка приемов экстренного извлечения пострадавшего из труднодоступного места, отработка основных приемов (пострадавший в сознании, пострадавший без сознания).</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>Тема 4 / практика ← Тема 4 / практика</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно. Дополнительно тема извлечения и перемещения отражена в теории темы 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="64" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>Отработка приемов перемещения пострадавших на руках одним, двумя и более участниками оказания первой помощи. Отработка приемов переноски пострадавших с травмами головы, шеи, груди, живота, таза, конечностей и позвоночника.</t>
+        </is>
+      </c>
+      <c r="C71" s="19" t="inlineStr">
+        <is>
+          <t>Отработка приемов перемещения пострадавших на руках одним, 2 и более участниками оказания первой помощи. Отработка приемов перемещения пострадавших с травмами головы, шеи, груди, спины, живота, таза, конечностей и позвоночника.</t>
+        </is>
+      </c>
+      <c r="D71" s="19" t="inlineStr">
+        <is>
+          <t>Тема 4 / практика ← Тема 4 / практика</t>
+        </is>
+      </c>
+      <c r="E71" s="19" t="inlineStr">
+        <is>
           <t>Переформулирование</t>
         </is>
       </c>
-      <c r="F65" s="19" t="inlineStr">
-        <is>
-          <t>Добавлен опрос; пункт перенесён в практику темы 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="40" customHeight="1">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>4.14</t>
-        </is>
-      </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="inlineStr">
-        <is>
-          <t>Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr">
-        <is>
-          <t>Тема 4 / практика ← Тема 3 / практика</t>
-        </is>
-      </c>
-      <c r="E66" s="14" t="inlineStr">
-        <is>
-          <t>Перенесено</t>
-        </is>
-      </c>
-      <c r="F66" s="14" t="inlineStr">
-        <is>
-          <t>Формулировка сохранена; блок перемещён из практики старой темы 3 в практику новой темы 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="53" customHeight="1">
-      <c r="A67" s="19" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="B67" s="19" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения повязок при наличии инородного предмета в ране живота, груди, конечностей. (старая тема 3; частично также в новой теме 2)</t>
-        </is>
-      </c>
-      <c r="C67" s="19" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения повязок на рану при выпадении органов брюшной полости, при наличии инородного предмета в ране живота, груди, спины, конечностей.</t>
-        </is>
-      </c>
-      <c r="D67" s="19" t="inlineStr">
-        <is>
-          <t>Тема 4 / практика ← Тема 3 / практика</t>
-        </is>
-      </c>
-      <c r="E67" s="19" t="inlineStr">
-        <is>
-          <t>Расширение / детализация</t>
-        </is>
-      </c>
-      <c r="F67" s="19" t="inlineStr">
-        <is>
-          <t>Добавлены: выпадение органов брюшной полости; область «спина». (Параллельно в теме 2 осталась давящая повязка с фиксацией инородного предмета.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="62" customHeight="1">
-      <c r="A68" s="19" t="inlineStr">
-        <is>
-          <t>4.16</t>
-        </is>
-      </c>
-      <c r="B68" s="19" t="inlineStr">
-        <is>
-          <t>Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий).</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий, обездвиживание руками травмированных частей тела).</t>
-        </is>
-      </c>
-      <c r="D68" s="19" t="inlineStr">
-        <is>
-          <t>Тема 4 / практика ← Тема 3 / практика</t>
-        </is>
-      </c>
-      <c r="E68" s="19" t="inlineStr">
-        <is>
-          <t>Расширение / детализация</t>
-        </is>
-      </c>
-      <c r="F68" s="19" t="inlineStr">
-        <is>
-          <t>Добавлен способ: «обездвиживание руками травмированных частей тела».</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="40" customHeight="1">
-      <c r="A69" s="14" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>Отработка приемов фиксации шейного отдела позвоночника.</t>
-        </is>
-      </c>
-      <c r="C69" s="14" t="inlineStr">
-        <is>
-          <t>Отработка приемов фиксации шейного отдела позвоночника.</t>
-        </is>
-      </c>
-      <c r="D69" s="14" t="inlineStr">
-        <is>
-          <t>Тема 4 / практика ← Тема 3 / практика</t>
-        </is>
-      </c>
-      <c r="E69" s="14" t="inlineStr">
-        <is>
-          <t>Перенесено</t>
-        </is>
-      </c>
-      <c r="F69" s="14" t="inlineStr">
-        <is>
-          <t>Формулировка сохранена; перенесено в тему 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="40" customHeight="1">
-      <c r="A70" s="13" t="inlineStr">
-        <is>
-          <t>4.18</t>
-        </is>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения повязок при ожогах различных областей тела. Применение местного охлаждения.</t>
-        </is>
-      </c>
-      <c r="C70" s="13" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения повязок при ожогах различных областей тела. Применение местного охлаждения.</t>
-        </is>
-      </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="F71" s="19" t="inlineStr">
+        <is>
+          <t>«двумя» → «2»; «переноски» → «перемещения»; добавлена «спина».</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="48" customHeight="1">
+      <c r="A72" s="19" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>Отработка приемов оказания психологической поддержки пострадавшим при различных острых стрессовых реакциях. Способы самопомощи в экстремальных ситуациях.</t>
+        </is>
+      </c>
+      <c r="C72" s="19" t="inlineStr">
+        <is>
+          <t>Отработка приемов оказания психологической поддержки пострадавших при различных острых психологических реакциях на стресс. Способы самопомощи в экстремальных ситуациях.</t>
+        </is>
+      </c>
+      <c r="D72" s="19" t="inlineStr">
         <is>
           <t>Тема 4 / практика ← Тема 4 / практика</t>
         </is>
       </c>
-      <c r="E70" s="13" t="inlineStr">
-        <is>
-          <t>Без изменений (по смыслу)</t>
-        </is>
-      </c>
-      <c r="F70" s="13" t="inlineStr">
-        <is>
-          <t>Дословно сохранено.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="40" customHeight="1">
-      <c r="A71" s="13" t="inlineStr">
-        <is>
-          <t>4.19</t>
-        </is>
-      </c>
-      <c r="B71" s="13" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения термоизолирующей повязки при отморожениях.</t>
-        </is>
-      </c>
-      <c r="C71" s="13" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения термоизолирующей повязки при отморожениях.</t>
-        </is>
-      </c>
-      <c r="D71" s="13" t="inlineStr">
-        <is>
-          <t>Тема 4 / практика ← Тема 4 / практика</t>
-        </is>
-      </c>
-      <c r="E71" s="13" t="inlineStr">
-        <is>
-          <t>Без изменений (по смыслу)</t>
-        </is>
-      </c>
-      <c r="F71" s="13" t="inlineStr">
-        <is>
-          <t>Дословно сохранено.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="52" customHeight="1">
-      <c r="A72" s="13" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
-        <is>
-          <t>Отработка приемов придания оптимального положения тела пострадавшему при отсутствии сознания, травмах различных областей тела, значительной кровопотере.</t>
-        </is>
-      </c>
-      <c r="C72" s="13" t="inlineStr">
-        <is>
-          <t>Отработка приемов придания оптимального положения тела пострадавшему при отсутствии сознания, травмах различных областей тела, значительной кровопотере.</t>
-        </is>
-      </c>
-      <c r="D72" s="13" t="inlineStr">
-        <is>
-          <t>Тема 4 / практика ← Тема 4 / практика</t>
-        </is>
-      </c>
-      <c r="E72" s="13" t="inlineStr">
-        <is>
-          <t>Без изменений (по смыслу)</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="inlineStr">
-        <is>
-          <t>Дословно сохранено.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="54" customHeight="1">
-      <c r="A73" s="13" t="inlineStr">
-        <is>
-          <t>4.21</t>
-        </is>
-      </c>
-      <c r="B73" s="13" t="inlineStr">
-        <is>
-          <t>Отработка приемов экстренного извлечения пострадавшего из труднодоступного места, отработка основных приемов (пострадавший в сознании, пострадавший без сознания).</t>
-        </is>
-      </c>
-      <c r="C73" s="13" t="inlineStr">
-        <is>
-          <t>Отработка приемов экстренного извлечения пострадавшего из труднодоступного места, отработка основных приемов (пострадавший в сознании, пострадавший без сознания).</t>
-        </is>
-      </c>
-      <c r="D73" s="13" t="inlineStr">
-        <is>
-          <t>Тема 4 / практика ← Тема 4 / практика</t>
-        </is>
-      </c>
-      <c r="E73" s="13" t="inlineStr">
-        <is>
-          <t>Без изменений (по смыслу)</t>
-        </is>
-      </c>
-      <c r="F73" s="13" t="inlineStr">
-        <is>
-          <t>Дословно сохранено. Дополнительно тема извлечения/перемещения теперь отражена и в теории темы 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="70" customHeight="1">
-      <c r="A74" s="19" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="B74" s="19" t="inlineStr">
-        <is>
-          <t>Отработка приемов перемещения пострадавших на руках одним, двумя и более участниками оказания первой помощи. Отработка приемов переноски пострадавших с травмами головы, шеи, груди, живота, таза, конечностей и позвоночника.</t>
-        </is>
-      </c>
-      <c r="C74" s="19" t="inlineStr">
-        <is>
-          <t>Отработка приемов перемещения пострадавших на руках одним, 2 и более участниками оказания первой помощи. Отработка приемов перемещения пострадавших с травмами головы, шеи, груди, спины, живота, таза, конечностей и позвоночника.</t>
-        </is>
-      </c>
-      <c r="D74" s="19" t="inlineStr">
-        <is>
-          <t>Тема 4 / практика ← Тема 4 / практика</t>
-        </is>
-      </c>
-      <c r="E74" s="19" t="inlineStr">
+      <c r="E72" s="19" t="inlineStr">
         <is>
           <t>Переформулирование</t>
         </is>
       </c>
-      <c r="F74" s="19" t="inlineStr">
-        <is>
-          <t>«двумя» → «2»; «переноски» → «перемещения»; добавлена «спина».</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="56" customHeight="1">
-      <c r="A75" s="19" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
-      <c r="B75" s="19" t="inlineStr">
-        <is>
-          <t>Отработка приемов оказания психологической поддержки пострадавшим при различных острых стрессовых реакциях. Способы самопомощи в экстремальных ситуациях.</t>
-        </is>
-      </c>
-      <c r="C75" s="19" t="inlineStr">
-        <is>
-          <t>Отработка приемов оказания психологической поддержки пострадавших при различных острых психологических реакциях на стресс. Способы самопомощи в экстремальных ситуациях.</t>
-        </is>
-      </c>
-      <c r="D75" s="19" t="inlineStr">
-        <is>
-          <t>Тема 4 / практика ← Тема 4 / практика</t>
-        </is>
-      </c>
-      <c r="E75" s="19" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-      <c r="F75" s="19" t="inlineStr">
+      <c r="F72" s="19" t="inlineStr">
         <is>
           <t>«пострадавшим» → «пострадавших»; «острых стрессовых реакциях» → «острых психологических реакциях на стресс».</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="15" t="inlineStr">
-        <is>
-          <t>ИСКЛЮЧЁННЫЕ ДЕТАЛИ СТАРОЙ ТЕМЫ 3 (травмы по областям) — свод исключения</t>
-        </is>
-      </c>
-      <c r="B76" s="16" t="n"/>
-      <c r="C76" s="16" t="n"/>
-      <c r="D76" s="16" t="n"/>
-      <c r="E76" s="16" t="n"/>
-      <c r="F76" s="16" t="n"/>
-    </row>
-    <row r="77" ht="40" customHeight="1">
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>ИСКЛЮЧЁННЫЕ ДЕТАЛИ ИСХОДНОЙ ТЕМЫ 3 (травмы по областям) — полные формулировки</t>
+        </is>
+      </c>
+      <c r="B73" s="16" t="n"/>
+      <c r="C73" s="16" t="n"/>
+      <c r="D73" s="16" t="n"/>
+      <c r="E73" s="16" t="n"/>
+      <c r="F73" s="16" t="n"/>
+    </row>
+    <row r="74" ht="48" customHeight="1">
+      <c r="A74" s="21" t="inlineStr">
+        <is>
+          <t>И.1</t>
+        </is>
+      </c>
+      <c r="B74" s="21" t="inlineStr">
+        <is>
+          <t>Травмы головы. Оказание первой помощи. Особенности ранений волосистой части головы. Особенности оказания первой помощи при травмах глаза и носа.</t>
+        </is>
+      </c>
+      <c r="C74" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="21" t="inlineStr">
+        <is>
+          <t>Тема 3 (исходная) / теория</t>
+        </is>
+      </c>
+      <c r="E74" s="21" t="inlineStr">
+        <is>
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="F74" s="21" t="inlineStr">
+        <is>
+          <t>Покрыто общей фразой «Травмы различных областей тела».</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="64" customHeight="1">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>И.2</t>
+        </is>
+      </c>
+      <c r="B75" s="21" t="inlineStr">
+        <is>
+          <t>Травмы шеи, оказание первой помощи. Временная остановка наружного кровотечения при травмах шеи. Фиксация шейного отдела позвоночника (вручную, подручными средствами, с использованием медицинских изделий).</t>
+        </is>
+      </c>
+      <c r="C75" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D75" s="21" t="inlineStr">
+        <is>
+          <t>Тема 3 (исходная) / теория</t>
+        </is>
+      </c>
+      <c r="E75" s="21" t="inlineStr">
+        <is>
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="F75" s="21" t="inlineStr">
+        <is>
+          <t>Кровотечение шеи отрабатывается в практике темы 2; фиксация шеи — в практике темы 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="64" customHeight="1">
+      <c r="A76" s="21" t="inlineStr">
+        <is>
+          <t>И.3</t>
+        </is>
+      </c>
+      <c r="B76" s="21" t="inlineStr">
+        <is>
+          <t>Травмы груди, оказание первой помощи. Основные проявления травмы груди, особенности наложения повязок при травме груди, наложение окклюзионной (герметизирующей) повязки. Особенности наложения повязки на рану груди с инородным телом.</t>
+        </is>
+      </c>
+      <c r="C76" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D76" s="21" t="inlineStr">
+        <is>
+          <t>Тема 3 (исходная) / теория</t>
+        </is>
+      </c>
+      <c r="E76" s="21" t="inlineStr">
+        <is>
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="F76" s="21" t="inlineStr">
+        <is>
+          <t>Практика по окклюзионной повязке и инородному предмету сохранена в теме 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="112" customHeight="1">
       <c r="A77" s="21" t="inlineStr">
         <is>
-          <t>И.1</t>
+          <t>И.4</t>
         </is>
       </c>
       <c r="B77" s="21" t="inlineStr">
         <is>
-          <t>Травмы головы… Особенности ранений волосистой части головы… травмы глаза и носа.</t>
+          <t>Травмы живота и таза, основные проявления. Оказание первой помощи.
+Закрытая травма живота с признаками внутреннего кровотечения. Оказание первой помощи. Особенности наложения повязок на рану при выпадении органов брюшной полости, при наличии инородного тела в ране.</t>
         </is>
       </c>
       <c r="C77" s="21" t="inlineStr">
@@ -3081,7 +3073,7 @@
       </c>
       <c r="D77" s="21" t="inlineStr">
         <is>
-          <t>Тема 3 (стар.) / теория</t>
+          <t>Тема 3 (исходная) / теория</t>
         </is>
       </c>
       <c r="E77" s="21" t="inlineStr">
@@ -3091,29 +3083,29 @@
       </c>
       <c r="F77" s="21" t="inlineStr">
         <is>
-          <t>Детализация травм головы/глаза/носа убрана; покрыто общей фразой «Травмы различных областей тела».</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="40" customHeight="1">
+          <t>Практика по выпадению органов и инородному предмету сохранена в теме 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="48" customHeight="1">
       <c r="A78" s="21" t="inlineStr">
         <is>
-          <t>И.2</t>
+          <t>И.5</t>
         </is>
       </c>
       <c r="B78" s="21" t="inlineStr">
         <is>
-          <t>Травмы шеи… Временная остановка наружного кровотечения при травмах шеи. Фиксация шейного отдела…</t>
+          <t>Травмы конечностей, оказание первой помощи. Понятие "иммобилизация". Способы иммобилизации при травме конечностей.</t>
         </is>
       </c>
       <c r="C78" s="21" t="inlineStr">
         <is>
-          <t>— (кровотечение шеи — в теме 2; фиксация шеи — в практике темы 4)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D78" s="21" t="inlineStr">
         <is>
-          <t>Тема 3 (стар.) / теория</t>
+          <t>Тема 3 (исходная) / теория</t>
         </is>
       </c>
       <c r="E78" s="21" t="inlineStr">
@@ -3123,29 +3115,29 @@
       </c>
       <c r="F78" s="21" t="inlineStr">
         <is>
-          <t>Теоретическая детализация травм шеи удалена; навыки распределены по другим разделам.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="40" customHeight="1">
+          <t>Практика по переломам и иммобилизации сохранена и расширена в теме 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="48" customHeight="1">
       <c r="A79" s="21" t="inlineStr">
         <is>
-          <t>И.3</t>
+          <t>И.6</t>
         </is>
       </c>
       <c r="B79" s="21" t="inlineStr">
         <is>
-          <t>Травмы груди… окклюзионная повязка… инородное тело в ране груди.</t>
+          <t>Травмы позвоночника. Оказание первой помощи.</t>
         </is>
       </c>
       <c r="C79" s="21" t="inlineStr">
         <is>
-          <t>— (практика темы 4)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D79" s="21" t="inlineStr">
         <is>
-          <t>Тема 3 (стар.) / теория</t>
+          <t>Тема 3 (исходная) / теория</t>
         </is>
       </c>
       <c r="E79" s="21" t="inlineStr">
@@ -3155,121 +3147,25 @@
       </c>
       <c r="F79" s="21" t="inlineStr">
         <is>
-          <t>Теория свёрнута; практика сохранена в теме 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="43" customHeight="1">
-      <c r="A80" s="21" t="inlineStr">
-        <is>
-          <t>И.4</t>
-        </is>
-      </c>
-      <c r="B80" s="21" t="inlineStr">
-        <is>
-          <t>Травмы живота и таза… закрытая травма живота с признаками внутреннего кровотечения… выпадение органов… инородное тело.</t>
-        </is>
-      </c>
-      <c r="C80" s="21" t="inlineStr">
-        <is>
-          <t>— (частично практика темы 4: выпадение органов / инородный предмет)</t>
-        </is>
-      </c>
-      <c r="D80" s="21" t="inlineStr">
-        <is>
-          <t>Тема 3 (стар.) / теория</t>
-        </is>
-      </c>
-      <c r="E80" s="21" t="inlineStr">
-        <is>
-          <t>Исключено</t>
-        </is>
-      </c>
-      <c r="F80" s="21" t="inlineStr">
-        <is>
-          <t>Теоретическая детализация удалена; отдельные практические приёмы сохранены.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="40" customHeight="1">
-      <c r="A81" s="21" t="inlineStr">
-        <is>
-          <t>И.5</t>
-        </is>
-      </c>
-      <c r="B81" s="21" t="inlineStr">
-        <is>
-          <t>Травмы конечностей… Понятие «иммобилизация». Способы иммобилизации…</t>
-        </is>
-      </c>
-      <c r="C81" s="21" t="inlineStr">
-        <is>
-          <t>— (практика темы 4: переломы / иммобилизация)</t>
-        </is>
-      </c>
-      <c r="D81" s="21" t="inlineStr">
-        <is>
-          <t>Тема 3 (стар.) / теория</t>
-        </is>
-      </c>
-      <c r="E81" s="21" t="inlineStr">
-        <is>
-          <t>Исключено</t>
-        </is>
-      </c>
-      <c r="F81" s="21" t="inlineStr">
-        <is>
-          <t>Термин «иммобилизация» и способы убраны из теории; практика сохранена и расширена.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="40" customHeight="1">
-      <c r="A82" s="21" t="inlineStr">
-        <is>
-          <t>И.6</t>
-        </is>
-      </c>
-      <c r="B82" s="21" t="inlineStr">
-        <is>
-          <t>Травмы позвоночника. Оказание первой помощи.</t>
-        </is>
-      </c>
-      <c r="C82" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="21" t="inlineStr">
-        <is>
-          <t>Тема 3 (стар.) / теория</t>
-        </is>
-      </c>
-      <c r="E82" s="21" t="inlineStr">
-        <is>
-          <t>Исключено</t>
-        </is>
-      </c>
-      <c r="F82" s="21" t="inlineStr">
-        <is>
-          <t>Отдельный теоретический пункт удалён; позвоночник упоминается в практике перемещения пострадавших.</t>
+          <t>Позвоночник упоминается в практике перемещения пострадавших.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F82"/>
+  <autoFilter ref="A1:F79"/>
   <mergeCells count="14">
-    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A73:F73"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
@@ -3283,13 +3179,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="75" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3300,12 +3196,12 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Формулировка</t>
+          <t>Полная формулировка</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Где (новая/старая привязка)</t>
+          <t>Где (привязка)</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
@@ -3314,10 +3210,10 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>ДОБАВЛЕНО в редакции N 805 от 30.06.2026</t>
+          <t>ДОБАВЛЕНО в редакции N 805 от 30.06.2026 — полные формулировки</t>
         </is>
       </c>
       <c r="B2" s="18" t="n"/>
@@ -3342,7 +3238,7 @@
       </c>
       <c r="D3" s="20" t="inlineStr">
         <is>
-          <t>Новые акценты вместо понятия «первая помощь»</t>
+          <t>Вместо понятия «первая помощь»</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3474,7 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Опрос пострадавшего (в связке с подробным осмотром).</t>
+          <t>Подробный осмотр и опрос пострадавшего. / Проведение подробного осмотра и опроса пострадавшего.</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -3586,7 +3482,11 @@
           <t>Тема 4 / теория и практика</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>Добавлен опрос</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
@@ -3596,7 +3496,7 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>Обездвиживание руками травмированных частей тела (в иммобилизации).</t>
+          <t>…обездвиживание руками травмированных частей тела).</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -3604,37 +3504,45 @@
           <t>Тема 4 / практика</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr"/>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>Добавлено</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>Область «спина» / «смежные зоны» в ряде практических пунктов по кровотечению и перемещению.</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>Темы 2 и 4 / практика</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>ИСКЛЮЧЕНО / СУЩЕСТВЕННО СНЯТО из исходной редакции</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
-    </row>
-    <row r="20" ht="36" customHeight="1">
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>Дополнение к иммобилизации</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>ИСКЛЮЧЕНО / СУЩЕСТВЕННО СНЯТО из исходной редакции — полные формулировки</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>Организация оказания первой помощи в Российской Федерации. Нормативно-правовая база, определяющая права, обязанности и ответственность при оказании первой помощи.</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>Тема 1 / теория</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>Заменено сжатой формулой</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
       <c r="A20" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3642,7 +3550,7 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Нормативно-правовая база, определяющая права, обязанности и ответственность…</t>
+          <t>Понятие "первая помощь".</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -3650,13 +3558,9 @@
           <t>Тема 1 / теория</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>Сжато до общей формулы</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+      <c r="D20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21" ht="40" customHeight="1">
       <c r="A21" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3664,7 +3568,7 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>Понятие «первая помощь».</t>
+          <t>Современные наборы средств и устройств, использующиеся для оказания первой помощи (аптечка первой помощи (автомобильная), аптечка для оказания первой помощи работникам и др.).</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -3672,9 +3576,13 @@
           <t>Тема 1 / теория</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr"/>
-    </row>
-    <row r="22" ht="36" customHeight="1">
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>Примеры аптечек убраны</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
       <c r="A22" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3682,7 +3590,7 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>Примеры аптечек: автомобильная; для оказания первой помощи работникам.</t>
+          <t>Общая последовательность действий на месте происшествия с наличием пострадавших. Соблюдение правил личной безопасности и обеспечение безопасных условий для оказания первой помощи (возможные факторы риска, их устранение). Простейшие меры профилактики инфекционных заболеваний, передающихся при непосредственном контакте с человеком, его кровью и другими биологическими жидкостями.</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -3690,9 +3598,13 @@
           <t>Тема 1 / теория</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr"/>
-    </row>
-    <row r="23" ht="36" customHeight="1">
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>Заменено краткой формулой</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
       <c r="A23" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3700,17 +3612,21 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>Общая последовательность действий на месте происшествия… правила личной безопасности… факторы риска…</t>
+          <t>Понятия "кровотечение", "острая кровопотеря". Признаки различных видов наружного кровотечения (артериального, венозного, капиллярного, смешанного). Способы временной остановки наружного кровотечения: пальцевое прижатие артерии, наложение жгута, максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>Тема 1 / теория</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr"/>
-    </row>
-    <row r="24" ht="36" customHeight="1">
+          <t>Тема 3 (исходная) / теория</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>Частично осталось обобщённо и в практике</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
       <c r="A24" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3718,17 +3634,17 @@
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Детализация профилактики инфекций (контакт, кровь, биологические жидкости).</t>
+          <t>Оказание первой помощи при носовом кровотечении.</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Тема 1 / теория</t>
+          <t>Тема 3 (исходная) / теория</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="40" customHeight="1">
       <c r="A25" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3736,17 +3652,17 @@
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>Классификация наружных кровотечений: артериальное, венозное, капиллярное, смешанное.</t>
+          <t>Понятие о травматическом шоке, причины и признаки. Мероприятия, предупреждающие развитие травматического шока.</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>Тема 3 стар. / теория</t>
+          <t>Тема 3 (исходная) / теория</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr"/>
     </row>
-    <row r="26" ht="36" customHeight="1">
+    <row r="26" ht="40" customHeight="1">
       <c r="A26" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3754,21 +3670,21 @@
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>Перечень способов остановки кровотечения в теории (пальцевое прижатие, жгут, сгибание, прямое давление, давящая повязка).</t>
+          <t>Отработка приемов временной остановки наружного кровотечения при ранениях головы, шеи, груди, живота, таза и конечностей с помощью пальцевого прижатия артерий (сонной, подключичной, подмышечной, плечевой, бедренной); наложение табельного и импровизированного кровоостанавливающего жгута (жгута-закрутки, ремня), максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Тема 3 стар. / теория</t>
+          <t>Тема 3 (исходная) / практика</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>Частично осталось в практике</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
+          <t>Заменено новыми практическими пунктами темы 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
       <c r="A27" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3776,17 +3692,21 @@
       </c>
       <c r="B27" s="21" t="inlineStr">
         <is>
-          <t>Оказание первой помощи при носовом кровотечении.</t>
+          <t>Основные признаки жизни у пострадавшего. Причины нарушения дыхания и кровообращения. Способы проверки сознания, дыхания, кровообращения у пострадавшего.</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>Тема 3 стар. / теория</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr"/>
-    </row>
-    <row r="28" ht="36" customHeight="1">
+          <t>Тема 2 (исходная) / теория</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>Заменено: «Определение признаков жизни.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
       <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3794,17 +3714,17 @@
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>Понятие о травматическом шоке, причины и признаки; предупреждение шока.</t>
+          <t>Ошибки и осложнения, возникающие при выполнении реанимационных мероприятий. Показания к прекращению реанимации. Мероприятия, выполняемые после прекращения реанимации.</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Тема 3 стар. / теория</t>
+          <t>Тема 2 (исходная) / теория</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr"/>
     </row>
-    <row r="29" ht="36" customHeight="1">
+    <row r="29" ht="40" customHeight="1">
       <c r="A29" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3812,17 +3732,17 @@
       </c>
       <c r="B29" s="21" t="inlineStr">
         <is>
-          <t>Пальцевое прижатие артерий (сонной, подключичной, подмышечной, плечевой, бедренной) в практике.</t>
+          <t>Особенности реанимации у детей.</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>Тема 3 стар. / практика</t>
+          <t>Тема 2 (исходная) / теория</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr"/>
     </row>
-    <row r="30" ht="36" customHeight="1">
+    <row r="30" ht="40" customHeight="1">
       <c r="A30" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3830,17 +3750,21 @@
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>Максимальное сгибание конечности в суставе в практике.</t>
+          <t>Порядок оказания первой помощи при частичном и полном нарушении проходимости верхних дыхательных путей, вызванном инородным телом у пострадавших в сознании, без сознания. Особенности оказания первой помощи тучному пострадавшему, беременной женщине и ребенку.</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Тема 3 стар. / практика</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
-    </row>
-    <row r="31" ht="36" customHeight="1">
+          <t>Тема 2 (исходная) / теория</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>Заменено обобщённой фразой</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
       <c r="A31" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3848,17 +3772,17 @@
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>Причины нарушения дыхания и кровообращения; способы проверки сознания/дыхания/кровообращения (как развёрнутая теория).</t>
+          <t>Травмы головы. Оказание первой помощи. Особенности ранений волосистой части головы. Особенности оказания первой помощи при травмах глаза и носа.</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>Тема 2 стар. / теория</t>
+          <t>Тема 3 (исходная) / теория</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr"/>
     </row>
-    <row r="32" ht="36" customHeight="1">
+    <row r="32" ht="40" customHeight="1">
       <c r="A32" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3866,17 +3790,17 @@
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>Ошибки и осложнения реанимации; показания к прекращению; мероприятия после прекращения.</t>
+          <t>Травмы шеи, оказание первой помощи. Временная остановка наружного кровотечения при травмах шеи. Фиксация шейного отдела позвоночника (вручную, подручными средствами, с использованием медицинских изделий).</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Тема 2 стар. / теория</t>
+          <t>Тема 3 (исходная) / теория</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr"/>
     </row>
-    <row r="33" ht="36" customHeight="1">
+    <row r="33" ht="40" customHeight="1">
       <c r="A33" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3884,17 +3808,17 @@
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t>Особенности реанимации у детей.</t>
+          <t>Травмы груди, оказание первой помощи. Основные проявления травмы груди, особенности наложения повязок при травме груди, наложение окклюзионной (герметизирующей) повязки. Особенности наложения повязки на рану груди с инородным телом.</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>Тема 2 стар. / теория</t>
+          <t>Тема 3 (исходная) / теория</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr"/>
     </row>
-    <row r="34" ht="36" customHeight="1">
+    <row r="34" ht="40" customHeight="1">
       <c r="A34" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3902,17 +3826,18 @@
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>Частичное/полное нарушение проходимости; сознание/без сознания; особенности у тучного, беременной, ребёнка.</t>
+          <t>Травмы живота и таза, основные проявления. Оказание первой помощи.
+Закрытая травма живота с признаками внутреннего кровотечения. Оказание первой помощи. Особенности наложения повязок на рану при выпадении органов брюшной полости, при наличии инородного тела в ране.</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Тема 2 стар. / теория</t>
+          <t>Тема 3 (исходная) / теория</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr"/>
     </row>
-    <row r="35" ht="36" customHeight="1">
+    <row r="35" ht="40" customHeight="1">
       <c r="A35" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3920,17 +3845,17 @@
       </c>
       <c r="B35" s="21" t="inlineStr">
         <is>
-          <t>Детальный теоретический разбор травм головы, шеи, груди, живота/таза, конечностей, позвоночника.</t>
+          <t>Травмы конечностей, оказание первой помощи. Понятие "иммобилизация". Способы иммобилизации при травме конечностей.</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>Тема 3 стар. / теория</t>
+          <t>Тема 3 (исходная) / теория</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr"/>
     </row>
-    <row r="36" ht="36" customHeight="1">
+    <row r="36" ht="40" customHeight="1">
       <c r="A36" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3938,17 +3863,17 @@
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>Детализация ожогов (поверхностные/глубокие, ожог ВДП), факторов перегревания, видов холодовой травмы.</t>
+          <t>Травмы позвоночника. Оказание первой помощи.</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Тема 4 стар. / теория</t>
+          <t>Тема 3 (исходная) / теория</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr"/>
     </row>
-    <row r="37" ht="36" customHeight="1">
+    <row r="37" ht="40" customHeight="1">
       <c r="A37" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3956,17 +3881,23 @@
       </c>
       <c r="B37" s="21" t="inlineStr">
         <is>
-          <t>Пути попадания ядов; признаки острого отравления; помощь по путям поступления.</t>
+          <t>Виды ожогов, их признаки. Понятие о поверхностных и глубоких ожогах. Ожог верхних дыхательных путей, основные проявления. Оказание первой помощи.
+Перегревание, факторы, способствующие его развитию. Основные проявления, оказание первой помощи.
+Холодовая травма, ее виды. Основные проявления переохлаждения (гипотермии), отморожения, оказание первой помощи.</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>Тема 4 стар. / теория</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="inlineStr"/>
-    </row>
-    <row r="38" ht="36" customHeight="1">
+          <t>Тема 4 (исходная) / теория</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>Заменено обобщённой фразой о термических поражениях</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
       <c r="A38" s="21" t="inlineStr">
         <is>
           <t>Исключено</t>
@@ -3974,19 +3905,47 @@
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>Развёрнутые цели/принципы оптимальных положений, контроля состояния и психологической поддержки.</t>
+          <t>Отравления, пути попадания ядов в организм. Признаки острого отравления. Оказание первой помощи при попадании отравляющих веществ в организм через дыхательные пути, пищеварительный тракт, через кожу.</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>Тема 4 стар. / теория</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr"/>
+          <t>Тема 4 (исходная) / теория</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>Заменено словом «Отравления.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>Цель и принципы придания пострадавшим оптимальных положений тела. Оптимальные положения тела пострадавшего с травмами груди, живота, таза, конечностей, с потерей сознания, с признаками кровопотери.
+Способы контроля состояния пострадавшего, находящегося в сознании, без сознания.
+Психологическая поддержка. Цели оказания психологической поддержки. Общие принципы общения с пострадавшими, простые приемы их психологической поддержки.</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>Тема 4 (исходная) / теория</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>Заменено одной комплексной фразой</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3999,12 +3958,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="75" customWidth="1" min="2" max="2"/>
+    <col width="75" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4015,16 +3974,16 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Исходная редакция (полный текст блока)</t>
+          <t>Исходная редакция — полный текст блока</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Редакция N 805 от 30.06.2026 (полный текст блока)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
+          <t>Редакция N 805 от 30.06.2026 — полный текст блока</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="70" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Тема 1 — название</t>
@@ -4041,7 +4000,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="280" customHeight="1">
+    <row r="3" ht="320" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Тема 1 — теория</t>
@@ -4050,7 +4009,7 @@
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Организация оказания первой помощи в Российской Федерации. Нормативно-правовая база, определяющая права, обязанности и ответственность при оказании первой помощи.
-Понятие «первая помощь». Перечень состояний, при которых оказывается первая помощь, перечень мероприятий по ее оказанию.
+Понятие "первая помощь". Перечень состояний, при которых оказывается первая помощь, перечень мероприятий по ее оказанию.
 Современные наборы средств и устройств, использующиеся для оказания первой помощи (аптечка первой помощи (автомобильная), аптечка для оказания первой помощи работникам и др.). Основные компоненты, их назначение.
 Общая последовательность действий на месте происшествия с наличием пострадавших. Соблюдение правил личной безопасности и обеспечение безопасных условий для оказания первой помощи (возможные факторы риска, их устранение). Простейшие меры профилактики инфекционных заболеваний, передающихся при непосредственном контакте с человеком, его кровью и другими биологическими жидкостями.
 Основные правила вызова скорой медицинской помощи и других специальных служб, сотрудники которых обязаны оказывать первую помощь.</t>
@@ -4068,7 +4027,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="70" customHeight="1">
       <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Блок реанимации — название</t>
@@ -4085,7 +4044,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="269" customHeight="1">
+    <row r="5" ht="288" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Блок реанимации — теория</t>
@@ -4094,7 +4053,7 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Основные признаки жизни у пострадавшего. Причины нарушения дыхания и кровообращения. Способы проверки сознания, дыхания, кровообращения у пострадавшего.
-Современный алгоритм проведения сердечно-легочной реанимации (далее — реанимация). Техника проведения искусственного дыхания и давления руками на грудину пострадавшего при проведении реанимации.
+Современный алгоритм проведения сердечно-легочной реанимации (далее - реанимация). Техника проведения искусственного дыхания и давления руками на грудину пострадавшего при проведении реанимации.
 Ошибки и осложнения, возникающие при выполнении реанимационных мероприятий. Показания к прекращению реанимации. Мероприятия, выполняемые после прекращения реанимации.
 Особенности реанимации у детей.
 Порядок оказания первой помощи при частичном и полном нарушении проходимости верхних дыхательных путей, вызванном инородным телом у пострадавших в сознании, без сознания. Особенности оказания первой помощи тучному пострадавшему, беременной женщине и ребенку.</t>
@@ -4111,7 +4070,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="217" customHeight="1">
+    <row r="6" ht="274" customHeight="1">
       <c r="A6" s="22" t="inlineStr">
         <is>
           <t>Блок реанимации — практика</t>
@@ -4123,7 +4082,7 @@
 Отработка навыков определения сознания у пострадавшего.
 Отработка приемов восстановления проходимости верхних дыхательных путей. Оценка признаков жизни у пострадавшего.
 Отработка вызова скорой медицинской помощи, других специальных служб.
-Отработка приемов искусственного дыхания «рот ко рту», «рот к носу» с применением устройств для искусственного дыхания.
+Отработка приемов искусственного дыхания "рот ко рту", "рот к носу" с применением устройств для искусственного дыхания.
 Отработка приемов давления руками на грудину пострадавшего.
 Выполнение алгоритма реанимации.
 Отработка приема перевода пострадавшего в устойчивое боковое положение.
@@ -4139,14 +4098,14 @@
 Оценка признаков жизни у пострадавшего.
 Отработка вызова скорой медицинской помощи, других специальных служб.
 Отработка приемов давления руками на грудину пострадавшего.
-Отработка приемов искусственного дыхания «рот ко рту», «рот к носу» с применением устройств для искусственного дыхания.
+Отработка приемов искусственного дыхания "рот ко рту", "рот к носу" с применением устройств для искусственного дыхания.
 Отработка приема перевода пострадавшего в устойчивое боковое положение.
 Отработка алгоритма применения автоматического наружного дефибриллятора.
 Отработка приемов удаления инородного тела из верхних дыхательных путей пострадавшего.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="70" customHeight="1">
       <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Блок кровотечений — название</t>
@@ -4154,7 +4113,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Тема 3. Оказание первой помощи при наружных кровотечениях и травмах (часть о кровотечениях)</t>
+          <t>Тема 3. Оказание первой помощи при наружных кровотечениях и травмах</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -4163,16 +4122,16 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="187" customHeight="1">
+    <row r="8" ht="200" customHeight="1">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t>Блок кровотечений — теория</t>
+          <t>Блок кровотечений — теория (кровотечения)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Цель и порядок выполнения обзорного осмотра пострадавшего.
-Понятия «кровотечение», «острая кровопотеря». Признаки различных видов наружного кровотечения (артериального, венозного, капиллярного, смешанного). Способы временной остановки наружного кровотечения: пальцевое прижатие артерии, наложение жгута, максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.
+Понятия "кровотечение", "острая кровопотеря". Признаки различных видов наружного кровотечения (артериального, венозного, капиллярного, смешанного). Способы временной остановки наружного кровотечения: пальцевое прижатие артерии, наложение жгута, максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.
 Оказание первой помощи при носовом кровотечении.
 Понятие о травматическом шоке, причины и признаки. Мероприятия, предупреждающие развитие травматического шока.</t>
         </is>
@@ -4187,7 +4146,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="153" customHeight="1">
+    <row r="9" ht="209" customHeight="1">
       <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Блок кровотечений — практика</t>
@@ -4209,47 +4168,95 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="320" customHeight="1">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Тема 4 — название</t>
+          <t>Тема 3 (исходная) — теория травм (перешло в тему 4)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Тема 4. Оказание первой помощи при прочих состояниях</t>
+          <t>Цель и последовательность подробного осмотра пострадавшего. Основные состояния, с которыми может столкнуться участник оказания первой помощи.
+Травмы головы. Оказание первой помощи. Особенности ранений волосистой части головы. Особенности оказания первой помощи при травмах глаза и носа.
+Травмы шеи, оказание первой помощи. Временная остановка наружного кровотечения при травмах шеи. Фиксация шейного отдела позвоночника (вручную, подручными средствами, с использованием медицинских изделий).
+Травмы груди, оказание первой помощи. Основные проявления травмы груди, особенности наложения повязок при травме груди, наложение окклюзионной (герметизирующей) повязки. Особенности наложения повязки на рану груди с инородным телом.
+Травмы живота и таза, основные проявления. Оказание первой помощи.
+Закрытая травма живота с признаками внутреннего кровотечения. Оказание первой помощи. Особенности наложения повязок на рану при выпадении органов брюшной полости, при наличии инородного тела в ране.
+Травмы конечностей, оказание первой помощи. Понятие "иммобилизация". Способы иммобилизации при травме конечностей.
+Травмы позвоночника. Оказание первой помощи.</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Тема 4. Оказание первой помощи при травмах, ранениях, поражениях и прочих состояниях</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="126" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>Тема 4 — теория</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>[из темы 3] Цель и последовательность подробного осмотра… Основные состояния…
-Травмы головы / шеи / груди / живота и таза / конечностей / позвоночника (детально).
-[из темы 4] Виды ожогов… Перегревание… Холодовая травма…
-Отравления…
-Цель и принципы придания оптимальных положений…
-Способы контроля состояния…
-Психологическая поддержка…
-Принципы передачи пострадавшего бригаде СМП…</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Подробный осмотр и опрос пострадавшего.
 Основные состояния, с которыми может столкнуться участник оказания первой помощи.
-Травмы различных областей тела.
-Поражения, вызванные термическими факторами, — ожоги, перегревание, отморожение, переохлаждение.
+Травмы различных областей тела.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="196" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Тема 3 (исходная) — практика травм (перешло в тему 4)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Проведение подробного осмотра пострадавшего.
+Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.
+Отработка приемов наложения повязок при наличии инородного предмета в ране живота, груди, конечностей.
+Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий).
+Отработка приемов фиксации шейного отдела позвоночника.</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Проведение подробного осмотра и опроса пострадавшего.
+Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.
+Отработка приемов наложения повязок на рану при выпадении органов брюшной полости, при наличии инородного предмета в ране живота, груди, спины, конечностей.
+Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий, обездвиживание руками травмированных частей тела).
+Отработка приемов фиксации шейного отдела позвоночника.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Тема 4 — название</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Тема 4. Оказание первой помощи при прочих состояниях</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Тема 4. Оказание первой помощи при травмах, ранениях, поражениях и прочих состояниях</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="320" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Тема 4 — теория (прочие состояния + новые позиции)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Виды ожогов, их признаки. Понятие о поверхностных и глубоких ожогах. Ожог верхних дыхательных путей, основные проявления. Оказание первой помощи.
+Перегревание, факторы, способствующие его развитию. Основные проявления, оказание первой помощи.
+Холодовая травма, ее виды. Основные проявления переохлаждения (гипотермии), отморожения, оказание первой помощи.
+Отравления, пути попадания ядов в организм. Признаки острого отравления. Оказание первой помощи при попадании отравляющих веществ в организм через дыхательные пути, пищеварительный тракт, через кожу.
+Цель и принципы придания пострадавшим оптимальных положений тела. Оптимальные положения тела пострадавшего с травмами груди, живота, таза, конечностей, с потерей сознания, с признаками кровопотери.
+Способы контроля состояния пострадавшего, находящегося в сознании, без сознания.
+Психологическая поддержка. Цели оказания психологической поддержки. Общие принципы общения с пострадавшими, простые приемы их психологической поддержки.
+Принципы передачи пострадавшего бригаде скорой медицинской помощи, другим специальным службам, сотрудники которых обязаны оказывать первую помощь.</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Поражения, вызванные термическими факторами, - ожоги, перегревание, отморожение, переохлаждение.
 Поражения, вызванные химическими и электрическими факторами, излучением.
 Отравления.
 Укусы и ужаливания ядовитых животных.
@@ -4261,31 +4268,30 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="98" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>Тема 4 — практика</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>[из темы 3] подробный осмотр; окклюзионная повязка; инородный предмет; переломы/иммобилизация; фиксация шеи.
-[из темы 4] повязки при ожогах; термоизолирующая повязка; оптимальное положение; экстренное извлечение; перемещение/переноска; психологическая поддержка при острых стрессовых реакциях.</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Проведение подробного осмотра и опроса пострадавшего.
-Окклюзионная повязка при ранении грудной клетки.
-Повязки при выпадении органов брюшной полости и инородном предмете (живот, грудь, спина, конечности).
-Переломы / иммобилизация (+ обездвиживание руками).
-Фиксация шейного отдела позвоночника.
-Повязки при ожогах + местное охлаждение.
-Термоизолирующая повязка при отморожениях.
-Оптимальное положение тела.
-Экстренное извлечение.
-Перемещение на руках; перемещение при травмах (+ спина).
-Психологическая поддержка при острых психологических реакциях на стресс; самопомощь.</t>
+    <row r="14" ht="318" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Тема 4 — практика (прочие состояния)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок при ожогах различных областей тела. Применение местного охлаждения.
+Отработка приемов наложения термоизолирующей повязки при отморожениях.
+Отработка приемов придания оптимального положения тела пострадавшему при отсутствии сознания, травмах различных областей тела, значительной кровопотере.
+Отработка приемов экстренного извлечения пострадавшего из труднодоступного места, отработка основных приемов (пострадавший в сознании, пострадавший без сознания).
+Отработка приемов перемещения пострадавших на руках одним, двумя и более участниками оказания первой помощи. Отработка приемов переноски пострадавших с травмами головы, шеи, груди, живота, таза, конечностей и позвоночника.
+Отработка приемов оказания психологической поддержки пострадавшим при различных острых стрессовых реакциях. Способы самопомощи в экстремальных ситуациях.</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок при ожогах различных областей тела. Применение местного охлаждения.
+Отработка приемов наложения термоизолирующей повязки при отморожениях.
+Отработка приемов придания оптимального положения тела пострадавшему при отсутствии сознания, травмах различных областей тела, значительной кровопотере.
+Отработка приемов экстренного извлечения пострадавшего из труднодоступного места, отработка основных приемов (пострадавший в сознании, пострадавший без сознания).
+Отработка приемов перемещения пострадавших на руках одним, 2 и более участниками оказания первой помощи. Отработка приемов перемещения пострадавших с травмами головы, шеи, груди, спины, живота, таза, конечностей и позвоночника.
+Отработка приемов оказания психологической поддержки пострадавших при различных острых психологических реакциях на стресс. Способы самопомощи в экстремальных ситуациях.</t>
         </is>
       </c>
     </row>

--- a/Анализ_изменений_Приложение_2_ПП_2464.xlsx
+++ b/Анализ_изменений_Приложение_2_ПП_2464.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Пояснение" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="По порядку ред. 30.06.2026" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Для копирования (Стало→Было)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Для копирования" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'По порядку ред. 30.06.2026'!$A$1:$F$80</definedName>
@@ -31,13 +31,7 @@
     </font>
     <font>
       <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <sz val="10"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -46,7 +40,13 @@
     </font>
     <font>
       <name val="Times New Roman"/>
-      <sz val="12"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="10">
@@ -125,32 +125,32 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -521,49 +521,43 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Порядок строк в таблице соответствует порядку Приложения № 2 в редакции с изменениями N 805 от 30.06.2026: Тема 1 → теория; Тема 2 → теория → практика; Тема 3 → теория → практика; Тема 4 → теория → практика. Столбец «Стало» — формулировка новой редакции; «Было» — соответствующая формулировка исходной редакции (или «—», если пункт добавлен).</t>
+          <t>Порядок строк = Приложение № 2 в ред. N 805 от 30.06.2026 (Тема 1 → теория; Тема 2 → теория → практика; Тема 3 → теория → практика; Тема 4 → теория → практика). Колонка «Характер изменения (детально)» описывает конкретно, что изменено, добавлено или исключено в каждой теме/подтеме.</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3"/>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Как копировать</t>
-        </is>
-      </c>
-    </row>
+    <row r="4"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1) Открыть лист «Для копирования (Стало→Было)» или файл КОПИРОВАТЬ_В_EXCEL.txt</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Колонки для копирования</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2) Выделить таблицу → Ctrl+C → вставить в Excel/Word</t>
+          <t>№ | Раздел | Стало | Было | Вид изменения | Характер изменения (детально)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Лист «По порядку ред. 30.06.2026» — полный анализ с разделами и комментариями.</t>
+          <t>Файл КОПИРОВАТЬ_В_EXCEL.txt — Ctrl+A → Ctrl+C → вставить в Excel</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="A1:B4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -579,11 +573,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -609,12 +603,12 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Характер изменения</t>
+          <t>Вид изменения</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Комментарий</t>
+          <t>Характер изменения (детально)</t>
         </is>
       </c>
     </row>
@@ -630,7 +624,7 @@
       <c r="E2" s="5" t="n"/>
       <c r="F2" s="5" t="n"/>
     </row>
-    <row r="3" ht="40" customHeight="1">
+    <row r="3" ht="50" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>1</t>
@@ -658,14 +652,14 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Название темы сохранено.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
+          <t>Название темы сохранено дословно. Содержание теоретического занятия внутри темы существенно переработано (см. п. 1.1–1.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Теоретическое занятие по теме 1  ←  было: Теоретическое занятие по теме 1</t>
+          <t>Теоретическое занятие по теме 1  ←  было: Теоретическое занятие по теме 1  |  Заголовок теоретического занятия сохранён. Изменён состав и формулировки пунктов внутри занятия.</t>
         </is>
       </c>
       <c r="B4" s="8" t="n"/>
@@ -674,7 +668,7 @@
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="8" t="n"/>
     </row>
-    <row r="5" ht="40" customHeight="1">
+    <row r="5" ht="50" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -702,11 +696,11 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Формулировка сжата и переставлена. Исключены слова о правах, обязанностях и ответственности.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
+          <t>Порядок слов изменён: сначала «нормативно-правовая база», затем «организация». Исключено уточнение, что база определяет права, обязанности и ответственность при оказании первой помощи. Смысл сведён к общей формуле без детализации правового статуса участников.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>1.2</t>
@@ -734,11 +728,11 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Убраны примеры конкретных аптечек. Введена обобщённая терминология.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
+          <t>Вместо «современные наборы средств и устройств» введена терминология «укладки, наборы, комплекты и аптечки». Исключены примеры: аптечка первой помощи (автомобильная) и аптечка для оказания первой помощи работникам. Фраза о компонентах и назначении сохранена по смыслу (с лёгкой правкой пунктуации: «и их назначение»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>1.3</t>
@@ -766,11 +760,11 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Вместо понятия «первая помощь» — порядок и приоритетность. Перечень состояний/мероприятий вынесен в следующий пункт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
+          <t>Исключено изучение понятия «первая помощь» как отдельного элемента. Введены два новых акцента: «порядок оказания первой помощи» и «приоритетность оказания первой помощи». Перечень состояний и мероприятий из прежней фразы вынесен в следующий самостоятельный пункт (1.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>1.4</t>
@@ -793,16 +787,16 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Переформулирование</t>
+          <t>Переформулирование / расширение</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Перечень сохранён; добавлена «последовательность их выполнения»; понятие «первая помощь» убрано.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1">
+          <t>Перечень состояний сохранён. Перечень мероприятий переформулирован («по ее оказанию» → «по оказанию первой помощи»). Добавлено требование изучать последовательность выполнения мероприятий. Понятие «первая помощь» в этом пункте не воспроизводится.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>1.5</t>
@@ -830,11 +824,11 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Детализация безопасности и профилактики свёрнута.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
+          <t>Исключены: общая последовательность действий на месте происшествия; правила личной безопасности; указание на возможные факторы риска и их устранение; детализация путей передачи инфекций (непосредственный контакт, кровь, биологические жидкости). Оставлена краткая формула про безопасные условия и профилактику инфекционных заболеваний. Часть смысла о последовательности действий покрыта п. 1.3 (порядок и приоритетность).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>1.6</t>
@@ -862,11 +856,11 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>Новый теоретический пункт. Ранее близкие навыки — только в практике темы 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
+          <t>Новый теоретический пункт темы 1. В исходной редакции аналогичное содержание отсутствовало в теории темы 1 и отрабатывалось только практически в теме 4 (экстренное извлечение и перемещение пострадавших).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -889,12 +883,12 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Переформулирование</t>
+          <t>Переформулирование (минорное)</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Убрано слово «Основные»; «и других» → «других».</t>
+          <t>Убрано слово «Основные». Союз «и других» заменён перечислением через запятую («других»). Смысл и отсылка к обязанности сотрудников специальных служб сохранены.</t>
         </is>
       </c>
     </row>
@@ -910,7 +904,7 @@
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
     </row>
-    <row r="13" ht="40" customHeight="1">
+    <row r="13" ht="50" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>2</t>
@@ -938,14 +932,14 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Из прежней темы 3 выделен блок кровотечений; травмы ушли в тему 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
+          <t>В новой редакции кровотечения выделены в отдельную тему 2. Прежняя тема 3 («кровотечения и травмы») разделена: кровотечения → тема 2; травмы → тема 4. Номер 2 освобождён за счёт переноса блока реанимации в тему 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Теоретическое занятие по теме 2  ←  было: Теоретическое занятие по теме 3</t>
+          <t>Теоретическое занятие по теме 2  ←  было: Теоретическое занятие по теме 3  |  Теория по кровотечениям перенесена из темы 3 в тему 2. Состав пунктов сужен и обобщён: убраны носовое кровотечение и травматический шок; добавлены последовательность остановки и остановка при ранениях разных областей.</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
@@ -954,7 +948,7 @@
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
     </row>
-    <row r="15" ht="40" customHeight="1">
+    <row r="15" ht="50" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -982,11 +976,11 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Добавлены «Кровотечение» и указание на нескольких пострадавших.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
+          <t>Убраны слова «цель и порядок выполнения». В начало пункта добавлено слово «Кровотечение» как тематический заход. Добавлено указание на осмотр нескольких пострадавших — «(пострадавших)».</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>2.2</t>
@@ -1014,11 +1008,11 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Убраны понятия-термины и классификация видов кровотечения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="40" customHeight="1">
+          <t>Исключены отдельные понятия «кровотечение» и «острая кровопотеря» как термины для изучения. Исключена классификация видов наружного кровотечения (артериальное, венозное, капиллярное, смешанное). Оставлена общая формулировка о признаках наружного кровотечения и кровопотери. Способы остановки вынесены в п. 2.3 без перечня техник.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -1046,11 +1040,11 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Перечень конкретных способов убран из теории; общая формулировка сохранена.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
+          <t>В теории сохранены только «способы временной остановки» без перечисления: пальцевое прижатие артерии, наложение жгута, максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки. Часть способов сохранена и детализирована в практике (п. 2.7–2.9), но пальцевое прижатие и сгибание конечности из практики убраны.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
           <t>2.4</t>
@@ -1076,9 +1070,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19" ht="40" customHeight="1">
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Новый теоретический пункт: акцент на последовательности действий при остановке кровотечения. В исходной редакции отдельной формулировки не было.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="50" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -1104,12 +1102,16 @@
           <t>Добавлено</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Новый теоретический пункт о остановке кровотечения при ранениях разных областей тела. В исходной редакции близкий смысл был распределён по разбору травм по областям и по практике.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Практическое занятие по теме 2  ←  было: Практическое занятие по теме 3</t>
+          <t>Практическое занятие по теме 2  ←  было: Практическое занятие по теме 3  |  Практика по кровотечениям выделена в тему 2. Из прежней практики темы 3 сюда перенесены и переработаны пункты по обзорному осмотру, остановке кровотечения и инородному предмету. Пункты по подробному осмотру, окклюзионной повязке, переломам и фиксации шеи ушли в практику темы 4.</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
@@ -1118,7 +1120,7 @@
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
     </row>
-    <row r="21" ht="40" customHeight="1">
+    <row r="21" ht="50" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>2.6</t>
@@ -1141,16 +1143,16 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Переформулирование</t>
+          <t>Переформулирование (минорное)</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Добавлено «(пострадавших)».</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1">
+          <t>Добавлено указание на осмотр нескольких пострадавших — «(пострадавших)». Остальная формулировка сохранена.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="50" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>2.7</t>
@@ -1178,11 +1180,11 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Выделено прямое давление; добавлены спина и смежные зоны; убраны пальцевое прижатие, сгибание, таз.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="40" customHeight="1">
+          <t>Из единого перечня способов выделен отдельный навык — прямое давление на рану. Из областей ранения: убран таз; добавлены спина и смежные зоны. Из способов в этом пункте не упоминаются: пальцевое прижатие артерий, жгут, максимальное сгибание конечности, давящая повязка (жгут и давящая повязка вынесены в п. 2.8–2.9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="50" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
           <t>2.8</t>
@@ -1210,11 +1212,11 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Давящая повязка вынесена в отдельный пункт; добавлены спина и смежные зоны.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
+          <t>Давящая повязка вынесена в отдельный практический пункт. Области: голова, грудь, спина, живот, конечности и смежные зоны (шеи в перечне этого пункта нет; таз убран; спина и смежные зоны добавлены).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="50" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>2.9</t>
@@ -1242,11 +1244,11 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Жгуты вынесены в отдельный пункт; вместо «жгута-закрутки, ремня» — «жгутов разных конструкций».</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="40" customHeight="1">
+          <t>Наложение жгутов вынесено в отдельный пункт и ограничено ранением конечностей. Вместо конкретизации «жгута-закрутки, ремня» — «жгутов разных конструкций». Пальцевое прижатие артерий и максимальное сгибание конечности в суставе в новой практике не воспроизводятся.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="50" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>2.10</t>
@@ -1269,12 +1271,12 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Переформулирование</t>
+          <t>Переформулирование / уточнение</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Уточнён тип повязки; добавлена спина.</t>
+          <t>Уточнён тип повязки: не просто «повязки», а «давящая повязка с фиксацией инородного предмета». Добавлена область «спина». Параллельно сходный навык расширен в практике темы 4 (п. 4.15) за счёт выпадения органов брюшной полости.</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1292,7 @@
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
     </row>
-    <row r="27" ht="40" customHeight="1">
+    <row r="27" ht="50" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>3</t>
@@ -1318,14 +1320,14 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>Блок реанимации перенесён с темы 2 на тему 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
+          <t>Название темы по смыслу сохранено. Блок реанимации перенесён с номера 2 на номер 3. Содержание теории и практики внутри блока переработано (см. п. 3.1–3.17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Теоретическое занятие по теме 3  ←  было: Теоретическое занятие по теме 2</t>
+          <t>Теоретическое занятие по теме 3  ←  было: Теоретическое занятие по теме 2  |  Теория реанимации перенесена в тему 3. Исключены: ошибки/осложнения/прекращение реанимации; особенности реанимации у детей; детализация инородного тела (частичное/полное, сознание/без сознания, тучный/беременная/ребёнок). Добавлены: проходимость дыхательных путей; АНД; иные нарушения дыхания.</t>
         </is>
       </c>
       <c r="B28" s="8" t="n"/>
@@ -1334,7 +1336,7 @@
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
     </row>
-    <row r="29" ht="40" customHeight="1">
+    <row r="29" ht="50" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
           <t>3.1</t>
@@ -1360,9 +1362,13 @@
           <t>Сокращение / обобщение</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30" ht="40" customHeight="1">
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Три элемента исходной формулировки (признаки жизни; причины нарушения дыхания и кровообращения; способы проверки сознания, дыхания, кровообращения) сжаты до одной фразы «Определение признаков жизни». Детализация причин и способов проверки в теории не сохранена.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="50" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -1388,9 +1394,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr"/>
-    </row>
-    <row r="31" ht="40" customHeight="1">
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Новый отдельный теоретический пункт о восстановлении и поддержании проходимости дыхательных путей. В исходной редакции близкий смысл был в практике и в блоке об инородном теле, но отдельной теоретической формулировки не было.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="50" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
           <t>3.3</t>
@@ -1416,9 +1426,13 @@
           <t>Сокращение / обобщение</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr"/>
-    </row>
-    <row r="32" ht="40" customHeight="1">
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Убраны слова «современный алгоритм» и сокращение «далее - реанимация». Детализация техники искусственного дыхания и давления руками на грудину убрана из теории (сохранена в практике п. 3.13–3.14). Оставлена общая формулировка о технике СЛР.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="50" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
           <t>3.4</t>
@@ -1444,9 +1458,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33" ht="40" customHeight="1">
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Новый элемент программы: автоматический наружный дефибриллятор (АНД) в теоретическом курсе, с оговоркой «при его наличии». В исходной редакции отсутствовал.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="50" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
           <t>3.5</t>
@@ -1472,9 +1490,13 @@
           <t>Сокращение / обобщение</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr"/>
-    </row>
-    <row r="34" ht="40" customHeight="1">
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Убраны различия частичного и полного нарушения проходимости. Убраны различия «в сознании / без сознания». Убраны особенности оказания помощи тучному пострадавшему, беременной женщине и ребенку. Формулировка обобщена до одной фразы об инородном теле.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="50" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
           <t>3.6</t>
@@ -1500,12 +1522,16 @@
           <t>Добавлено</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>Новый общий пункт о прочих угрожающих нарушениях дыхания (помимо инородного тела). В исходной редакции отсутствовал.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Практическое занятие по теме 3  ←  было: Практическое занятие по теме 2</t>
+          <t>Практическое занятие по теме 3  ←  было: Практическое занятие по теме 2  |  Практика реанимации перенесена в тему 3. Изменён порядок: сначала последовательность реанимационных мероприятий и компрессии, затем искусственное дыхание. Добавлен алгоритм АНД. «Навыки» определения сознания заменены на «приемы». Оценка признаков жизни выделена отдельным абзацем.</t>
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
@@ -1514,7 +1540,7 @@
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
     </row>
-    <row r="36" ht="40" customHeight="1">
+    <row r="36" ht="50" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
           <t>3.7</t>
@@ -1542,11 +1568,11 @@
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Вынесено в начало практики.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="40" customHeight="1">
+          <t>«Выполнение алгоритма реанимации» заменено на «отработку последовательности выполнения реанимационных мероприятий» и вынесено в начало практического занятия (в исходной редакции пункт стоял после компрессий и искусственного дыхания).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="50" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
@@ -1572,9 +1598,13 @@
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38" ht="40" customHeight="1">
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно. Позиция в последовательности практики сохранена сразу после начала реанимационных мероприятий (в новой редакции — после п. 3.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="50" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
           <t>3.9</t>
@@ -1597,80 +1627,80 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Переформулирование</t>
+          <t>Переформулирование (минорное)</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>«навыков» → «приемов».</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="40" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+          <t>Слово «навыков» заменено на «приемов». Объект отработки (определение сознания у пострадавшего) без изменений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="50" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Тема 3 / Практическое занятие по теме 3</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>Отработка приемов восстановления проходимости верхних дыхательных путей.</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Отработка приемов восстановления проходимости верхних дыхательных путей. Оценка признаков жизни у пострадавшего.</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Оформлено отдельным абзацем; оценка признаков жизни — следующий пункт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="40" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>Структурное разделение</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>Прежний совмещённый абзац разделён на два пункта: восстановление проходимости (3.10) и оценка признаков жизни (3.11). Текст первой части сохранён дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="50" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>Тема 3 / Практическое занятие по теме 3</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>Оценка признаков жизни у пострадавшего.</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>Отработка приемов восстановления проходимости верхних дыхательных путей. Оценка признаков жизни у пострадавшего.</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>Вынесено в отдельный абзац.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="40" customHeight="1">
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>Структурное разделение</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>Фраза «Оценка признаков жизни у пострадавшего» вынесена в отдельный пункт. Содержание сохранено дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="50" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t>3.12</t>
@@ -1696,75 +1726,79 @@
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr"/>
-    </row>
-    <row r="42" ht="40" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="50" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>3.13</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Тема 3 / Практическое занятие по теме 3</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>Отработка приемов давления руками на грудину пострадавшего.</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>Отработка приемов искусственного дыхания "рот ко рту", "рот к носу" с применением устройств для искусственного дыхания.
 Отработка приемов давления руками на грудину пострадавшего.</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>В новой редакции компрессии идут раньше искусственного дыхания.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="40" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>Изменение порядка</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>Формулировка о давлении руками на грудину сохранена дословно, но в новой редакции стоит раньше искусственного дыхания (в исходной — после него). Это соответствует современной последовательности СЛР: компрессии → дыхание.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="50" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>3.14</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>Тема 3 / Практическое занятие по теме 3</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>Отработка приемов искусственного дыхания "рот ко рту", "рот к носу" с применением устройств для искусственного дыхания.</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>Отработка приемов искусственного дыхания "рот ко рту", "рот к носу" с применением устройств для искусственного дыхания.
 Отработка приемов давления руками на грудину пострадавшего.</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>Порядок изменён: после компрессий.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="40" customHeight="1">
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Изменение порядка</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>Формулировка об искусственном дыхании сохранена дословно, но перенесена после компрессий (п. 3.13). Содержание приёмов («рот ко рту», «рот к носу», устройства) без изменений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="50" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
           <t>3.15</t>
@@ -1790,9 +1824,13 @@
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr"/>
-    </row>
-    <row r="45" ht="40" customHeight="1">
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="50" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
           <t>3.16</t>
@@ -1818,9 +1856,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr"/>
-    </row>
-    <row r="46" ht="40" customHeight="1">
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>Новый практический навык — алгоритм применения АНД. Соответствует новому теоретическому пункту 3.4. В исходной редакции отсутствовал.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="50" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -1846,7 +1888,11 @@
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -1860,7 +1906,7 @@
       <c r="E47" s="5" t="n"/>
       <c r="F47" s="5" t="n"/>
     </row>
-    <row r="48" ht="40" customHeight="1">
+    <row r="48" ht="50" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
           <t>4</t>
@@ -1884,19 +1930,19 @@
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>Объединение тем</t>
+          <t>Объединение тем / расширение названия</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>В тему 4 включены травмы/ранения из прежней темы 3 и прочие состояния из прежней темы 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
+          <t>Название расширено: к «прочим состояниям» добавлены травмы, ранения и поражения. В тему 4 включены: травмы из прежней темы 3; прочие состояния из прежней темы 4; новые пункты (химия/электричество/излучение, укусы, судороги, лекарства, транспортировка).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="45" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Теоретическое занятие по теме 4  ←  было: Теоретическое занятие по теме 3 (травмы) + Теоретическое занятие по теме 4 (прочие состояния)</t>
+          <t>Теоретическое занятие по теме 4  ←  было: Теоретическое занятие по теме 3 (травмы) + Теоретическое занятие по теме 4 (прочие состояния)  |  Теория травм по областям тела свёрнута в одну фразу. Термические поражения, отравления, положения тела и психоподдержка обобщены. Добавлены химические/электрические поражения и излучение, укусы, судорожный приступ, помощь с лекарствами, транспортировка. Добавлен опрос пострадавшего.</t>
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
@@ -1905,7 +1951,7 @@
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
     </row>
-    <row r="50" ht="40" customHeight="1">
+    <row r="50" ht="50" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
           <t>4.1</t>
@@ -1928,16 +1974,16 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Переформулирование</t>
+          <t>Переформулирование / расширение</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>Добавлен опрос; убраны «цель и последовательность».</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="40" customHeight="1">
+          <t>Убраны «цель и последовательность». Добавлен «опрос» пострадавшего наряду с подробным осмотром. Фраза об основных состояниях вынесена в отдельный пункт 4.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="50" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -1960,16 +2006,16 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Без изменений</t>
+          <t>Без изменений (фраза)</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Фраза сохранена дословно отдельным абзацем.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="40" customHeight="1">
+          <t>Формулировка про основные состояния сохранена дословно и оформлена отдельным абзацем. Связанная с ней часть про цель и последовательность осмотра в п. 4.1 не сохранена.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="50" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
           <t>4.3</t>
@@ -2003,11 +2049,11 @@
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>Детальный разбор по областям свёрнут в одну фразу.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="40" customHeight="1">
+          <t>Семь развёрнутых блоков по областям (голова, шея, грудь, живот/таз, закрытая травма живота, конечности, позвоночник) заменены одной фразой. Из теории убраны: особенности ранений волосистой части головы, глаза и носа; фиксация шеи; окклюзионная повязка; инородное тело; выпадение органов; понятие «иммобилизация» и способы иммобилизации. Часть навыков сохранена в практике темы 4 (п. 4.14–4.17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="50" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -2035,9 +2081,13 @@
           <t>Сокращение / обобщение</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr"/>
-    </row>
-    <row r="54" ht="40" customHeight="1">
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>Три детальных блока (ожоги включая ожог ВДП и поверхностные/глубокие; перегревание с факторами развития; холодовая травма с гипотермией) сжаты в перечень термических поражений. Практические навыки по ожогам и отморожениям сохранены (п. 4.18–4.19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="50" customHeight="1">
       <c r="A54" s="10" t="inlineStr">
         <is>
           <t>4.5</t>
@@ -2063,9 +2113,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr"/>
-    </row>
-    <row r="55" ht="40" customHeight="1">
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>Новый теоретический пункт: химические и электрические поражения, излучение. В исходной редакции Приложения № 2 отсутствовал.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="50" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
           <t>4.6</t>
@@ -2091,9 +2145,13 @@
           <t>Сокращение / обобщение</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr"/>
-    </row>
-    <row r="56" ht="40" customHeight="1">
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>Убраны пути попадания ядов, признаки острого отравления и детализация помощи по путям поступления (дыхательные пути, пищеварительный тракт, кожа). Оставлено одно слово «Отравления.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="50" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -2119,9 +2177,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr"/>
-    </row>
-    <row r="57" ht="40" customHeight="1">
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>Новая тема теоретического курса. В исходной редакции отсутствовала.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="50" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -2147,9 +2209,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr"/>
-    </row>
-    <row r="58" ht="40" customHeight="1">
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>Новая тема теоретического курса. В исходной редакции отсутствовала.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="50" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -2175,9 +2241,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr"/>
-    </row>
-    <row r="59" ht="40" customHeight="1">
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>Новая тема теоретического курса. В исходной редакции отсутствовала.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="50" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
           <t>4.10</t>
@@ -2205,9 +2275,13 @@
           <t>Сокращение / обобщение</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr"/>
-    </row>
-    <row r="60" ht="40" customHeight="1">
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>Три развёрнутых блока сжаты в одну комплексную фразу. Убраны: цели и принципы придания положений; перечень оптимальных положений по видам травм/состояний; различия контроля при сознании и без сознания; цели психоподдержки, принципы общения и простые приёмы. Практика по положению тела и психоподдержке сохранена (п. 4.20, 4.23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="50" customHeight="1">
       <c r="A60" s="10" t="inlineStr">
         <is>
           <t>4.11</t>
@@ -2233,9 +2307,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr"/>
-    </row>
-    <row r="61" ht="40" customHeight="1">
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>Новый теоретический пункт. В исходной редакции близкий смысл был только в практике перемещения/переноски пострадавших, без отдельной теоретической формулировки «транспортировка».</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="50" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
           <t>4.12</t>
@@ -2261,12 +2339,16 @@
           <t>Переформулирование</t>
         </is>
       </c>
-      <c r="F61" s="9" t="inlineStr"/>
-    </row>
-    <row r="62" ht="22" customHeight="1">
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>Убрано слово «принципы». Добавлены: «выездной» характер бригады и «медицинская организация» как адресат передачи. Убрана отсылка к обязанности сотрудников специальных служб оказывать первую помощь.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="45" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Практическое занятие по теме 4  ←  было: Практическое занятие по теме 3 (травмы) + Практическое занятие по теме 4 (прочие состояния)</t>
+          <t>Практическое занятие по теме 4  ←  было: Практическое занятие по теме 3 (травмы) + Практическое занятие по теме 4 (прочие состояния)  |  В практику темы 4 объединены навыки из прежних тем 3 и 4. Добавлены: опрос; выпадение органов брюшной полости; спина; обездвиживание руками. Минорно изменены формулировки перемещения и психоподдержки.</t>
         </is>
       </c>
       <c r="B62" s="8" t="n"/>
@@ -2275,337 +2357,357 @@
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
     </row>
-    <row r="63" ht="40" customHeight="1">
-      <c r="A63" s="9" t="inlineStr">
+    <row r="63" ht="50" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>4.13</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>Тема 4 / Практическое занятие по теме 4</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>Проведение подробного осмотра и опроса пострадавшего.</t>
         </is>
       </c>
-      <c r="D63" s="9" t="inlineStr">
+      <c r="D63" s="11" t="inlineStr">
         <is>
           <t>Проведение подробного осмотра пострадавшего.</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>Переформулирование / перенос</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>Пункт перенесён из практики прежней темы 3 в практику темы 4. Добавлен опрос пострадавшего (согласовано с теорией п. 4.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="50" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>Тема 4 / Практическое занятие по теме 4</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>Перенесено (текст без изменений)</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно. Изменён только раздел: из практики прежней темы 3 → в практику новой темы 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="50" customHeight="1">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>Тема 4 / Практическое занятие по теме 4</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок на рану при выпадении органов брюшной полости, при наличии инородного предмета в ране живота, груди, спины, конечностей.</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок при наличии инородного предмета в ране живота, груди, конечностей.</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>Расширение / детализация</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Добавлено: наложение повязок при выпадении органов брюшной полости. Добавлена область «спина». Уточнено «повязок на рану». Параллельно в теме 2 (п. 2.10) осталась давящая повязка с фиксацией инородного предмета.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="50" customHeight="1">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>Тема 4 / Практическое занятие по теме 4</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий, обездвиживание руками травмированных частей тела).</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий).</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>Расширение / детализация</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>В перечень способов иммобилизации добавлено «обездвиживание руками травмированных частей тела». Остальные способы сохранены. Пункт перенесён из практики прежней темы 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="50" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>Тема 4 / Практическое занятие по теме 4</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>Отработка приемов фиксации шейного отдела позвоночника.</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>Отработка приемов фиксации шейного отдела позвоночника.</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>Перенесено (текст без изменений)</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно. Изменён только раздел: из практики прежней темы 3 → в практику новой темы 4. Теоретическая детализация фиксации шеи (вручную, подручными средствами, медизделия) из прежней темы 3 в теорию новой редакции не перенесена.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="50" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Тема 4 / Практическое занятие по теме 4</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок при ожогах различных областей тела. Применение местного охлаждения.</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок при ожогах различных областей тела. Применение местного охлаждения.</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно. Раздел (практика темы 4) совпадает с исходной редакцией.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="50" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Тема 4 / Практическое занятие по теме 4</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения термоизолирующей повязки при отморожениях.</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения термоизолирующей повязки при отморожениях.</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="50" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Тема 4 / Практическое занятие по теме 4</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов придания оптимального положения тела пострадавшему при отсутствии сознания, травмах различных областей тела, значительной кровопотере.</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов придания оптимального положения тела пострадавшему при отсутствии сознания, травмах различных областей тела, значительной кровопотере.</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно. Теория по этому блоку сокращена (п. 4.10), практика — без изменений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="50" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Тема 4 / Практическое занятие по теме 4</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов экстренного извлечения пострадавшего из труднодоступного места, отработка основных приемов (пострадавший в сознании, пострадавший без сознания).</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов экстренного извлечения пострадавшего из труднодоступного места, отработка основных приемов (пострадавший в сознании, пострадавший без сознания).</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно. Дополнительно тема извлечения/перемещения отражена в теории темы 1 (п. 1.6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="50" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>Тема 4 / Практическое занятие по теме 4</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов перемещения пострадавших на руках одним, 2 и более участниками оказания первой помощи. Отработка приемов перемещения пострадавших с травмами головы, шеи, груди, спины, живота, таза, конечностей и позвоночника.</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов перемещения пострадавших на руках одним, двумя и более участниками оказания первой помощи. Отработка приемов переноски пострадавших с травмами головы, шеи, груди, живота, таза, конечностей и позвоночника.</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
         <is>
           <t>Переформулирование</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
-        <is>
-          <t>Добавлен опрос; перенесено из практики прежней темы 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="40" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>4.14</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>«двумя» заменено на «2». Во второй фразе «переноски» заменено на «перемещения» (унификация термина). В перечень областей травм добавлена «спина».</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="50" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
         <is>
           <t>Тема 4 / Практическое занятие по теме 4</t>
         </is>
       </c>
-      <c r="C64" s="11" t="inlineStr">
-        <is>
-          <t>Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.</t>
-        </is>
-      </c>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>Перенесено</t>
-        </is>
-      </c>
-      <c r="F64" s="11" t="inlineStr">
-        <is>
-          <t>Формулировка без изменений; из практики прежней темы 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="40" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>Тема 4 / Практическое занятие по теме 4</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения повязок на рану при выпадении органов брюшной полости, при наличии инородного предмета в ране живота, груди, спины, конечностей.</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения повязок при наличии инородного предмета в ране живота, груди, конечностей.</t>
-        </is>
-      </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>Расширение / детализация</t>
-        </is>
-      </c>
-      <c r="F65" s="9" t="inlineStr">
-        <is>
-          <t>Добавлены выпадение органов брюшной полости и спина.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="40" customHeight="1">
-      <c r="A66" s="9" t="inlineStr">
-        <is>
-          <t>4.16</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Тема 4 / Практическое занятие по теме 4</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий, обездвиживание руками травмированных частей тела).</t>
-        </is>
-      </c>
-      <c r="D66" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий).</t>
-        </is>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>Расширение / детализация</t>
-        </is>
-      </c>
-      <c r="F66" s="9" t="inlineStr">
-        <is>
-          <t>Добавлено обездвиживание руками.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="40" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t>Тема 4 / Практическое занятие по теме 4</t>
-        </is>
-      </c>
-      <c r="C67" s="11" t="inlineStr">
-        <is>
-          <t>Отработка приемов фиксации шейного отдела позвоночника.</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>Отработка приемов фиксации шейного отдела позвоночника.</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="inlineStr">
-        <is>
-          <t>Перенесено</t>
-        </is>
-      </c>
-      <c r="F67" s="11" t="inlineStr">
-        <is>
-          <t>Формулировка без изменений; из практики прежней темы 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="40" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>4.18</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>Тема 4 / Практическое занятие по теме 4</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения повязок при ожогах различных областей тела. Применение местного охлаждения.</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения повязок при ожогах различных областей тела. Применение местного охлаждения.</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr"/>
-    </row>
-    <row r="69" ht="40" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>4.19</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>Тема 4 / Практическое занятие по теме 4</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения термоизолирующей повязки при отморожениях.</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения термоизолирующей повязки при отморожениях.</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr"/>
-    </row>
-    <row r="70" ht="40" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>Тема 4 / Практическое занятие по теме 4</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов придания оптимального положения тела пострадавшему при отсутствии сознания, травмах различных областей тела, значительной кровопотере.</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов придания оптимального положения тела пострадавшему при отсутствии сознания, травмах различных областей тела, значительной кровопотере.</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr"/>
-    </row>
-    <row r="71" ht="40" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>4.21</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>Тема 4 / Практическое занятие по теме 4</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов экстренного извлечения пострадавшего из труднодоступного места, отработка основных приемов (пострадавший в сознании, пострадавший без сознания).</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов экстренного извлечения пострадавшего из труднодоступного места, отработка основных приемов (пострадавший в сознании, пострадавший без сознания).</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr"/>
-    </row>
-    <row r="72" ht="40" customHeight="1">
-      <c r="A72" s="9" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>Тема 4 / Практическое занятие по теме 4</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов перемещения пострадавших на руках одним, 2 и более участниками оказания первой помощи. Отработка приемов перемещения пострадавших с травмами головы, шеи, груди, спины, живота, таза, конечностей и позвоночника.</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов перемещения пострадавших на руках одним, двумя и более участниками оказания первой помощи. Отработка приемов переноски пострадавших с травмами головы, шеи, груди, живота, таза, конечностей и позвоночника.</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов оказания психологической поддержки пострадавших при различных острых психологических реакциях на стресс. Способы самопомощи в экстремальных ситуациях.</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов оказания психологической поддержки пострадавшим при различных острых стрессовых реакциях. Способы самопомощи в экстремальных ситуациях.</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
         <is>
           <t>Переформулирование</t>
         </is>
       </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>«двумя» → «2»; «переноски» → «перемещения»; добавлена спина.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="40" customHeight="1">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>Тема 4 / Практическое занятие по теме 4</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов оказания психологической поддержки пострадавших при различных острых психологических реакциях на стресс. Способы самопомощи в экстремальных ситуациях.</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов оказания психологической поддержки пострадавшим при различных острых стрессовых реакциях. Способы самопомощи в экстремальных ситуациях.</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="inlineStr"/>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>«пострадавшим» → «пострадавших» (управление слова «поддержки»). «острых стрессовых реакциях» → «острых психологических реакциях на стресс». Фраза о самопомощи без изменений.</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
@@ -2619,7 +2721,7 @@
       <c r="E74" s="5" t="n"/>
       <c r="F74" s="5" t="n"/>
     </row>
-    <row r="75" ht="40" customHeight="1">
+    <row r="75" ht="50" customHeight="1">
       <c r="A75" s="12" t="inlineStr">
         <is>
           <t>И.1</t>
@@ -2642,16 +2744,16 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Исключено (нет в ред. от 30.06.2026)</t>
+          <t>Исключено</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>Как отдельное понятие убрано; частично перекрыто п. 1.3–1.4 новой редакции.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="40" customHeight="1">
+          <t>Как отдельный элемент программы убрано. Частично перекрыто новыми пунктами о порядке и приоритетности оказания первой помощи (п. 1.3) и перечнем состояний/мероприятий (п. 1.4), но само понятие больше не формулируется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="50" customHeight="1">
       <c r="A76" s="12" t="inlineStr">
         <is>
           <t>И.2</t>
@@ -2674,12 +2776,16 @@
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Исключено (нет в ред. от 30.06.2026)</t>
-        </is>
-      </c>
-      <c r="F76" s="12" t="inlineStr"/>
-    </row>
-    <row r="77" ht="40" customHeight="1">
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>Весь блок об ошибках, осложнениях, показаниях к прекращению реанимации и действиях после прекращения удалён из теории. В новой теме 3 аналога нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="50" customHeight="1">
       <c r="A77" s="12" t="inlineStr">
         <is>
           <t>И.3</t>
@@ -2702,12 +2808,16 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Исключено (нет в ред. от 30.06.2026)</t>
-        </is>
-      </c>
-      <c r="F77" s="12" t="inlineStr"/>
-    </row>
-    <row r="78" ht="40" customHeight="1">
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>Отдельный пункт об особенностях реанимации у детей удалён. В новой теме 3 аналога нет (в т.ч. не сохранена и детализация помощи ребёнку при инородном теле).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="50" customHeight="1">
       <c r="A78" s="12" t="inlineStr">
         <is>
           <t>И.4</t>
@@ -2730,12 +2840,16 @@
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Исключено (нет в ред. от 30.06.2026)</t>
-        </is>
-      </c>
-      <c r="F78" s="12" t="inlineStr"/>
-    </row>
-    <row r="79" ht="40" customHeight="1">
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>Отдельный пункт о носовом кровотечении удалён. В новой теме 2 (кровотечения) аналога нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="50" customHeight="1">
       <c r="A79" s="12" t="inlineStr">
         <is>
           <t>И.5</t>
@@ -2758,12 +2872,16 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Исключено (нет в ред. от 30.06.2026)</t>
-        </is>
-      </c>
-      <c r="F79" s="12" t="inlineStr"/>
-    </row>
-    <row r="80" ht="40" customHeight="1">
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>Тема травматического шока полностью исключена из Приложения № 2 новой редакции. Ни в теме 2, ни в теме 4 не воспроизведена.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="50" customHeight="1">
       <c r="A80" s="12" t="inlineStr">
         <is>
           <t>И.6</t>
@@ -2786,12 +2904,12 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>Исключено (нет в ред. от 30.06.2026)</t>
+          <t>Исключено</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>Заменено пунктами 2.7–2.9 новой редакции; пальцевое прижатие и сгибание конечности не сохранены.</t>
+          <t>Единый практический пункт заменён тремя пунктами новой темы 2 (2.7–2.9). Не сохранены: пальцевое прижатие конкретных артерий; максимальное сгибание конечности в суставе; уточнения «жгут-закрутка, ремень»; ранения таза. Сохранены в изменённом виде: прямое давление, давящая повязка, табельные/импровизированные жгуты.</t>
         </is>
       </c>
     </row>
@@ -2821,13 +2939,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2848,11 +2967,16 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Характер изменения</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
+          <t>Вид изменения</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Характер изменения (детально)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1</t>
@@ -2873,8 +2997,13 @@
           <t>Без изменений</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Название темы сохранено дословно. Содержание теоретического занятия внутри темы существенно переработано (см. п. 1.1–1.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -2895,8 +3024,13 @@
           <t>Сокращение / обобщение</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Порядок слов изменён: сначала «нормативно-правовая база», затем «организация». Исключено уточнение, что база определяет права, обязанности и ответственность при оказании первой помощи. Смысл сведён к общей формуле без детализации правового статуса участников.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>1.2</t>
@@ -2917,8 +3051,13 @@
           <t>Переформулирование</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Вместо «современные наборы средств и устройств» введена терминология «укладки, наборы, комплекты и аптечки». Исключены примеры: аптечка первой помощи (автомобильная) и аптечка для оказания первой помощи работникам. Фраза о компонентах и назначении сохранена по смыслу (с лёгкой правкой пунктуации: «и их назначение»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>1.3</t>
@@ -2939,8 +3078,13 @@
           <t>Существенная переработка</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Исключено изучение понятия «первая помощь» как отдельного элемента. Введены два новых акцента: «порядок оказания первой помощи» и «приоритетность оказания первой помощи». Перечень состояний и мероприятий из прежней фразы вынесен в следующий самостоятельный пункт (1.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>1.4</t>
@@ -2958,495 +3102,610 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
+          <t>Переформулирование / расширение</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Перечень состояний сохранён. Перечень мероприятий переформулирован («по ее оказанию» → «по оказанию первой помощи»). Добавлено требование изучать последовательность выполнения мероприятий. Понятие «первая помощь» в этом пункте не воспроизводится.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Обеспечение безопасных условий для оказания первой помощи. Профилактика инфекционных заболеваний при оказании первой помощи.</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Общая последовательность действий на месте происшествия с наличием пострадавших. Соблюдение правил личной безопасности и обеспечение безопасных условий для оказания первой помощи (возможные факторы риска, их устранение). Простейшие меры профилактики инфекционных заболеваний, передающихся при непосредственном контакте с человеком, его кровью и другими биологическими жидкостями.</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Сокращение / обобщение</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Исключены: общая последовательность действий на месте происшествия; правила личной безопасности; указание на возможные факторы риска и их устранение; детализация путей передачи инфекций (непосредственный контакт, кровь, биологические жидкости). Оставлена краткая формула про безопасные условия и профилактику инфекционных заболеваний. Часть смысла о последовательности действий покрыта п. 1.3 (порядок и приоритетность).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Извлечение пострадавших из труднодоступных мест и их перемещение в безопасное место.</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Новый теоретический пункт темы 1. В исходной редакции аналогичное содержание отсутствовало в теории темы 1 и отрабатывалось только практически в теме 4 (экстренное извлечение и перемещение пострадавших).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Правила вызова скорой медицинской помощи, других специальных служб, сотрудники которых обязаны оказывать первую помощь.</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Основные правила вызова скорой медицинской помощи и других специальных служб, сотрудники которых обязаны оказывать первую помощь.</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Переформулирование (минорное)</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Убрано слово «Основные». Союз «и других» заменён перечислением через запятую («других»). Смысл и отсылка к обязанности сотрудников специальных служб сохранены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Тема 2. Оказание первой помощи при наружных кровотечениях</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Тема 3. Оказание первой помощи при наружных кровотечениях и травмах</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Разделение темы / изменение нумерации</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>В новой редакции кровотечения выделены в отдельную тему 2. Прежняя тема 3 («кровотечения и травмы») разделена: кровотечения → тема 2; травмы → тема 4. Номер 2 освобождён за счёт переноса блока реанимации в тему 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Кровотечение. Обзорный осмотр пострадавшего (пострадавших).</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Цель и порядок выполнения обзорного осмотра пострадавшего.</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
           <t>Переформулирование</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Обеспечение безопасных условий для оказания первой помощи. Профилактика инфекционных заболеваний при оказании первой помощи.</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Общая последовательность действий на месте происшествия с наличием пострадавших. Соблюдение правил личной безопасности и обеспечение безопасных условий для оказания первой помощи (возможные факторы риска, их устранение). Простейшие меры профилактики инфекционных заболеваний, передающихся при непосредственном контакте с человеком, его кровью и другими биологическими жидкостями.</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Убраны слова «цель и порядок выполнения». В начало пункта добавлено слово «Кровотечение» как тематический заход. Добавлено указание на осмотр нескольких пострадавших — «(пострадавших)».</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Признаки наружного кровотечения и кровопотери.</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Понятия "кровотечение", "острая кровопотеря". Признаки различных видов наружного кровотечения (артериального, венозного, капиллярного, смешанного). Способы временной остановки наружного кровотечения: пальцевое прижатие артерии, наложение жгута, максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Сокращение / обобщение</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Извлечение пострадавших из труднодоступных мест и их перемещение в безопасное место.</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Исключены отдельные понятия «кровотечение» и «острая кровопотеря» как термины для изучения. Исключена классификация видов наружного кровотечения (артериальное, венозное, капиллярное, смешанное). Оставлена общая формулировка о признаках наружного кровотечения и кровопотери. Способы остановки вынесены в п. 2.3 без перечня техник.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Способы временной остановки наружного кровотечения.</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Понятия "кровотечение", "острая кровопотеря". Признаки различных видов наружного кровотечения (артериального, венозного, капиллярного, смешанного). Способы временной остановки наружного кровотечения: пальцевое прижатие артерии, наложение жгута, максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Сокращение / обобщение</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>В теории сохранены только «способы временной остановки» без перечисления: пальцевое прижатие артерии, наложение жгута, максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки. Часть способов сохранена и детализирована в практике (п. 2.7–2.9), но пальцевое прижатие и сгибание конечности из практики убраны.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Последовательность выполнения мероприятий по остановке кровотечения.</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>Добавлено</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Правила вызова скорой медицинской помощи, других специальных служб, сотрудники которых обязаны оказывать первую помощь.</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Основные правила вызова скорой медицинской помощи и других специальных служб, сотрудники которых обязаны оказывать первую помощь.</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Новый теоретический пункт: акцент на последовательности действий при остановке кровотечения. В исходной редакции отдельной формулировки не было.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Остановка кровотечения при ранениях различных областей тела.</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Новый теоретический пункт о остановке кровотечения при ранениях разных областей тела. В исходной редакции близкий смысл был распределён по разбору травм по областям и по практике.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Отработка проведения обзорного осмотра пострадавшего (пострадавших).</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Отработка проведения обзорного осмотра пострадавшего.</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Переформулирование (минорное)</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Добавлено указание на осмотр нескольких пострадавших — «(пострадавших)». Остальная формулировка сохранена.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Отработка временной остановки наружного кровотечения при ранении головы, шеи, груди, спины, живота, конечностей и смежных зон с помощью прямого давления на рану.</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов временной остановки наружного кровотечения при ранениях головы, шеи, груди, живота, таза и конечностей с помощью пальцевого прижатия артерий (сонной, подключичной, подмышечной, плечевой, бедренной); наложение табельного и импровизированного кровоостанавливающего жгута (жгута-закрутки, ремня), максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Существенная переработка</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Из единого перечня способов выделен отдельный навык — прямое давление на рану. Из областей ранения: убран таз; добавлены спина и смежные зоны. Из способов в этом пункте не упоминаются: пальцевое прижатие артерий, жгут, максимальное сгибание конечности, давящая повязка (жгут и давящая повязка вынесены в п. 2.8–2.9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Отработка наложения давящей повязки при ранении головы, груди, спины, живота, конечностей и смежных зон.</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов временной остановки наружного кровотечения при ранениях головы, шеи, груди, живота, таза и конечностей с помощью пальцевого прижатия артерий (сонной, подключичной, подмышечной, плечевой, бедренной); наложение табельного и импровизированного кровоостанавливающего жгута (жгута-закрутки, ремня), максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Существенная переработка</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Давящая повязка вынесена в отдельный практический пункт. Области: голова, грудь, спина, живот, конечности и смежные зоны (шеи в перечне этого пункта нет; таз убран; спина и смежные зоны добавлены).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения табельных и импровизированных кровоостанавливающих жгутов разных конструкций при ранении конечностей.</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов временной остановки наружного кровотечения при ранениях головы, шеи, груди, живота, таза и конечностей с помощью пальцевого прижатия артерий (сонной, подключичной, подмышечной, плечевой, бедренной); наложение табельного и импровизированного кровоостанавливающего жгута (жгута-закрутки, ремня), максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Существенная переработка</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Наложение жгутов вынесено в отдельный пункт и ограничено ранением конечностей. Вместо конкретизации «жгута-закрутки, ремня» — «жгутов разных конструкций». Пальцевое прижатие артерий и максимальное сгибание конечности в суставе в новой практике не воспроизводятся.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения давящей повязки с фиксацией инородного предмета в ране живота, груди, спины, конечностей.</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок при наличии инородного предмета в ране живота, груди, конечностей.</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Переформулирование / уточнение</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Уточнён тип повязки: не просто «повязки», а «давящая повязка с фиксацией инородного предмета». Добавлена область «спина». Параллельно сходный навык расширен в практике темы 4 (п. 4.15) за счёт выпадения органов брюшной полости.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Тема 3. Оказание первой помощи при отсутствии сознания, остановке дыхания и кровообращения</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Тема 2. Оказание первой помощи при отсутствии сознания, остановке дыхания и кровообращения</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Изменение нумерации</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Название темы по смыслу сохранено. Блок реанимации перенесён с номера 2 на номер 3. Содержание теории и практики внутри блока переработано (см. п. 3.1–3.17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Определение признаков жизни.</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Основные признаки жизни у пострадавшего. Причины нарушения дыхания и кровообращения. Способы проверки сознания, дыхания, кровообращения у пострадавшего.</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Сокращение / обобщение</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Три элемента исходной формулировки (признаки жизни; причины нарушения дыхания и кровообращения; способы проверки сознания, дыхания, кровообращения) сжаты до одной фразы «Определение признаков жизни». Детализация причин и способов проверки в теории не сохранена.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Восстановление и поддержание проходимости дыхательных путей.</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Новый отдельный теоретический пункт о восстановлении и поддержании проходимости дыхательных путей. В исходной редакции близкий смысл был в практике и в блоке об инородном теле, но отдельной теоретической формулировки не было.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Техника проведения сердечно-легочной реанимации.</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Современный алгоритм проведения сердечно-легочной реанимации (далее - реанимация). Техника проведения искусственного дыхания и давления руками на грудину пострадавшего при проведении реанимации.</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Сокращение / обобщение</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Убраны слова «современный алгоритм» и сокращение «далее - реанимация». Детализация техники искусственного дыхания и давления руками на грудину убрана из теории (сохранена в практике п. 3.13–3.14). Оставлена общая формулировка о технике СЛР.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Использование автоматического наружного дефибриллятора (при его наличии).</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Новый элемент программы: автоматический наружный дефибриллятор (АНД) в теоретическом курсе, с оговоркой «при его наличии». В исходной редакции отсутствовал.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Первая помощь при нарушении проходимости верхних дыхательных путей, вызванном инородным телом.</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Порядок оказания первой помощи при частичном и полном нарушении проходимости верхних дыхательных путей, вызванном инородным телом у пострадавших в сознании, без сознания. Особенности оказания первой помощи тучному пострадавшему, беременной женщине и ребенку.</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Сокращение / обобщение</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Убраны различия частичного и полного нарушения проходимости. Убраны различия «в сознании / без сознания». Убраны особенности оказания помощи тучному пострадавшему, беременной женщине и ребенку. Формулировка обобщена до одной фразы об инородном теле.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Первая помощь при иных угрожающих жизни и здоровью нарушениях дыхания.</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Новый общий пункт о прочих угрожающих нарушениях дыхания (помимо инородного тела). В исходной редакции отсутствовал.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Отработка последовательности выполнения реанимационных мероприятий.</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Выполнение алгоритма реанимации.</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Переформулирование</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Тема 2. Оказание первой помощи при наружных кровотечениях</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Тема 3. Оказание первой помощи при наружных кровотечениях и травмах</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Разделение темы / изменение нумерации</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Кровотечение. Обзорный осмотр пострадавшего (пострадавших).</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Цель и порядок выполнения обзорного осмотра пострадавшего.</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Признаки наружного кровотечения и кровопотери.</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Понятия "кровотечение", "острая кровопотеря". Признаки различных видов наружного кровотечения (артериального, венозного, капиллярного, смешанного). Способы временной остановки наружного кровотечения: пальцевое прижатие артерии, наложение жгута, максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Сокращение / обобщение</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Способы временной остановки наружного кровотечения.</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Понятия "кровотечение", "острая кровопотеря". Признаки различных видов наружного кровотечения (артериального, венозного, капиллярного, смешанного). Способы временной остановки наружного кровотечения: пальцевое прижатие артерии, наложение жгута, максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Сокращение / обобщение</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Последовательность выполнения мероприятий по остановке кровотечения.</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Добавлено</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Остановка кровотечения при ранениях различных областей тела.</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Добавлено</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Отработка проведения обзорного осмотра пострадавшего (пострадавших).</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Отработка проведения обзорного осмотра пострадавшего.</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Отработка временной остановки наружного кровотечения при ранении головы, шеи, груди, спины, живота, конечностей и смежных зон с помощью прямого давления на рану.</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов временной остановки наружного кровотечения при ранениях головы, шеи, груди, живота, таза и конечностей с помощью пальцевого прижатия артерий (сонной, подключичной, подмышечной, плечевой, бедренной); наложение табельного и импровизированного кровоостанавливающего жгута (жгута-закрутки, ремня), максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Существенная переработка</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Отработка наложения давящей повязки при ранении головы, груди, спины, живота, конечностей и смежных зон.</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов временной остановки наружного кровотечения при ранениях головы, шеи, груди, живота, таза и конечностей с помощью пальцевого прижатия артерий (сонной, подключичной, подмышечной, плечевой, бедренной); наложение табельного и импровизированного кровоостанавливающего жгута (жгута-закрутки, ремня), максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Существенная переработка</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения табельных и импровизированных кровоостанавливающих жгутов разных конструкций при ранении конечностей.</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов временной остановки наружного кровотечения при ранениях головы, шеи, груди, живота, таза и конечностей с помощью пальцевого прижатия артерий (сонной, подключичной, подмышечной, плечевой, бедренной); наложение табельного и импровизированного кровоостанавливающего жгута (жгута-закрутки, ремня), максимальное сгибание конечности в суставе, прямое давление на рану, наложение давящей повязки.</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Существенная переработка</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения давящей повязки с фиксацией инородного предмета в ране живота, груди, спины, конечностей.</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения повязок при наличии инородного предмета в ране живота, груди, конечностей.</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Тема 3. Оказание первой помощи при отсутствии сознания, остановке дыхания и кровообращения</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Тема 2. Оказание первой помощи при отсутствии сознания, остановке дыхания и кровообращения</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>Изменение нумерации</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Определение признаков жизни.</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Основные признаки жизни у пострадавшего. Причины нарушения дыхания и кровообращения. Способы проверки сознания, дыхания, кровообращения у пострадавшего.</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Сокращение / обобщение</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Восстановление и поддержание проходимости дыхательных путей.</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Добавлено</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Техника проведения сердечно-легочной реанимации.</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Современный алгоритм проведения сердечно-легочной реанимации (далее - реанимация). Техника проведения искусственного дыхания и давления руками на грудину пострадавшего при проведении реанимации.</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Сокращение / обобщение</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Использование автоматического наружного дефибриллятора (при его наличии).</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Добавлено</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Первая помощь при нарушении проходимости верхних дыхательных путей, вызванном инородным телом.</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Порядок оказания первой помощи при частичном и полном нарушении проходимости верхних дыхательных путей, вызванном инородным телом у пострадавших в сознании, без сознания. Особенности оказания первой помощи тучному пострадавшему, беременной женщине и ребенку.</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Сокращение / обобщение</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Первая помощь при иных угрожающих жизни и здоровью нарушениях дыхания.</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Добавлено</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Отработка последовательности выполнения реанимационных мероприятий.</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Выполнение алгоритма реанимации.</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>«Выполнение алгоритма реанимации» заменено на «отработку последовательности выполнения реанимационных мероприятий» и вынесено в начало практического занятия (в исходной редакции пункт стоял после компрессий и искусственного дыхания).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
@@ -3467,8 +3726,13 @@
           <t>Без изменений</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно. Позиция в последовательности практики сохранена сразу после начала реанимационных мероприятий (в новой редакции — после п. 3.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
           <t>3.9</t>
@@ -3486,55 +3750,70 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+          <t>Переформулирование (минорное)</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>Слово «навыков» заменено на «приемов». Объект отработки (определение сознания у пострадавшего) без изменений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>Отработка приемов восстановления проходимости верхних дыхательных путей.</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>Отработка приемов восстановления проходимости верхних дыхательных путей. Оценка признаков жизни у пострадавшего.</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Структурное разделение</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Прежний совмещённый абзац разделён на два пункта: восстановление проходимости (3.10) и оценка признаков жизни (3.11). Текст первой части сохранён дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Оценка признаков жизни у пострадавшего.</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Отработка приемов восстановления проходимости верхних дыхательных путей. Оценка признаков жизни у пострадавшего.</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Структурное разделение</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Фраза «Оценка признаков жизни у пострадавшего» вынесена в отдельный пункт. Содержание сохранено дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t>3.12</t>
@@ -3555,54 +3834,69 @@
           <t>Без изменений</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>3.13</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>Отработка приемов давления руками на грудину пострадавшего.</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>Отработка приемов искусственного дыхания "рот ко рту", "рот к носу" с применением устройств для искусственного дыхания.
 Отработка приемов давления руками на грудину пострадавшего.</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Изменение порядка</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>Формулировка о давлении руками на грудину сохранена дословно, но в новой редакции стоит раньше искусственного дыхания (в исходной — после него). Это соответствует современной последовательности СЛР: компрессии → дыхание.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>3.14</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Отработка приемов искусственного дыхания "рот ко рту", "рот к носу" с применением устройств для искусственного дыхания.</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>Отработка приемов искусственного дыхания "рот ко рту", "рот к носу" с применением устройств для искусственного дыхания.
 Отработка приемов давления руками на грудину пострадавшего.</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Изменение порядка</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Формулировка об искусственном дыхании сохранена дословно, но перенесена после компрессий (п. 3.13). Содержание приёмов («рот ко рту», «рот к носу», устройства) без изменений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
           <t>3.15</t>
@@ -3623,8 +3917,13 @@
           <t>Без изменений</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="36" customHeight="1">
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="48" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
           <t>3.16</t>
@@ -3645,8 +3944,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>Новый практический навык — алгоритм применения АНД. Соответствует новому теоретическому пункту 3.4. В исходной редакции отсутствовал.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="48" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -3667,8 +3971,13 @@
           <t>Без изменений</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
           <t>4</t>
@@ -3687,11 +3996,16 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Объединение тем</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
+          <t>Объединение тем / расширение названия</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>Название расширено: к «прочим состояниям» добавлены травмы, ранения и поражения. В тему 4 включены: травмы из прежней темы 3; прочие состояния из прежней темы 4; новые пункты (химия/электричество/излучение, укусы, судороги, лекарства, транспортировка).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
           <t>4.1</t>
@@ -3709,11 +4023,16 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="36" customHeight="1">
+          <t>Переформулирование / расширение</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Убраны «цель и последовательность». Добавлен «опрос» пострадавшего наряду с подробным осмотром. Фраза об основных состояниях вынесена в отдельный пункт 4.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="48" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -3731,11 +4050,16 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
+          <t>Без изменений (фраза)</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка про основные состояния сохранена дословно и оформлена отдельным абзацем. Связанная с ней часть про цель и последовательность осмотра в п. 4.1 не сохранена.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
           <t>4.3</t>
@@ -3762,8 +4086,13 @@
           <t>Сокращение / обобщение</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>Семь развёрнутых блоков по областям (голова, шея, грудь, живот/таз, закрытая травма живота, конечности, позвоночник) заменены одной фразой. Из теории убраны: особенности ранений волосистой части головы, глаза и носа; фиксация шеи; окклюзионная повязка; инородное тело; выпадение органов; понятие «иммобилизация» и способы иммобилизации. Часть навыков сохранена в практике темы 4 (п. 4.14–4.17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="48" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -3786,8 +4115,13 @@
           <t>Сокращение / обобщение</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>Три детальных блока (ожоги включая ожог ВДП и поверхностные/глубокие; перегревание с факторами развития; холодовая травма с гипотермией) сжаты в перечень термических поражений. Практические навыки по ожогам и отморожениям сохранены (п. 4.18–4.19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="48" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
           <t>4.5</t>
@@ -3808,8 +4142,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="36" customHeight="1">
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>Новый теоретический пункт: химические и электрические поражения, излучение. В исходной редакции Приложения № 2 отсутствовал.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
           <t>4.6</t>
@@ -3830,8 +4169,13 @@
           <t>Сокращение / обобщение</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="36" customHeight="1">
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>Убраны пути попадания ядов, признаки острого отравления и детализация помощи по путям поступления (дыхательные пути, пищеварительный тракт, кожа). Оставлено одно слово «Отравления.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="48" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -3852,8 +4196,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="36" customHeight="1">
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>Новая тема теоретического курса. В исходной редакции отсутствовала.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -3874,8 +4223,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="36" customHeight="1">
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>Новая тема теоретического курса. В исходной редакции отсутствовала.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -3896,8 +4250,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="36" customHeight="1">
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Новая тема теоретического курса. В исходной редакции отсутствовала.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
           <t>4.10</t>
@@ -3920,8 +4279,13 @@
           <t>Сокращение / обобщение</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>Три развёрнутых блока сжаты в одну комплексную фразу. Убраны: цели и принципы придания положений; перечень оптимальных положений по видам травм/состояний; различия контроля при сознании и без сознания; цели психоподдержки, принципы общения и простые приёмы. Практика по положению тела и психоподдержке сохранена (п. 4.20, 4.23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="48" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
           <t>4.11</t>
@@ -3942,8 +4306,13 @@
           <t>Добавлено</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>Новый теоретический пункт. В исходной редакции близкий смысл был только в практике перемещения/переноски пострадавших, без отдельной теоретической формулировки «транспортировка».</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
           <t>4.12</t>
@@ -3964,250 +4333,310 @@
           <t>Переформулирование</t>
         </is>
       </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>Убрано слово «принципы». Добавлены: «выездной» характер бригады и «медицинская организация» как адресат передачи. Убрана отсылка к обязанности сотрудников специальных служб оказывать первую помощь.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="48" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>4.13</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>Проведение подробного осмотра и опроса пострадавшего.</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>Проведение подробного осмотра пострадавшего.</t>
         </is>
       </c>
-      <c r="D52" s="9" t="inlineStr">
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>Переформулирование / перенос</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>Пункт перенесён из практики прежней темы 3 в практику темы 4. Добавлен опрос пострадавшего (согласовано с теорией п. 4.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="48" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Перенесено (текст без изменений)</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно. Изменён только раздел: из практики прежней темы 3 → в практику новой темы 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок на рану при выпадении органов брюшной полости, при наличии инородного предмета в ране живота, груди, спины, конечностей.</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок при наличии инородного предмета в ране живота, груди, конечностей.</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>Расширение / детализация</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>Добавлено: наложение повязок при выпадении органов брюшной полости. Добавлена область «спина». Уточнено «повязок на рану». Параллельно в теме 2 (п. 2.10) осталась давящая повязка с фиксацией инородного предмета.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий, обездвиживание руками травмированных частей тела).</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий).</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>Расширение / детализация</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>В перечень способов иммобилизации добавлено «обездвиживание руками травмированных частей тела». Остальные способы сохранены. Пункт перенесён из практики прежней темы 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="48" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>Отработка приемов фиксации шейного отдела позвоночника.</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>Отработка приемов фиксации шейного отдела позвоночника.</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>Перенесено (текст без изменений)</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно. Изменён только раздел: из практики прежней темы 3 → в практику новой темы 4. Теоретическая детализация фиксации шеи (вручную, подручными средствами, медизделия) из прежней темы 3 в теорию новой редакции не перенесена.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="48" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок при ожогах различных областей тела. Применение местного охлаждения.</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения повязок при ожогах различных областей тела. Применение местного охлаждения.</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно. Раздел (практика темы 4) совпадает с исходной редакцией.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="48" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения термоизолирующей повязки при отморожениях.</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов наложения термоизолирующей повязки при отморожениях.</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="48" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов придания оптимального положения тела пострадавшему при отсутствии сознания, травмах различных областей тела, значительной кровопотере.</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов придания оптимального положения тела пострадавшему при отсутствии сознания, травмах различных областей тела, значительной кровопотере.</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно. Теория по этому блоку сокращена (п. 4.10), практика — без изменений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="48" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов экстренного извлечения пострадавшего из труднодоступного места, отработка основных приемов (пострадавший в сознании, пострадавший без сознания).</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Отработка приемов экстренного извлечения пострадавшего из труднодоступного места, отработка основных приемов (пострадавший в сознании, пострадавший без сознания).</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Формулировка сохранена дословно. Дополнительно тема извлечения/перемещения отражена в теории темы 1 (п. 1.6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="48" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов перемещения пострадавших на руках одним, 2 и более участниками оказания первой помощи. Отработка приемов перемещения пострадавших с травмами головы, шеи, груди, спины, живота, таза, конечностей и позвоночника.</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов перемещения пострадавших на руках одним, двумя и более участниками оказания первой помощи. Отработка приемов переноски пострадавших с травмами головы, шеи, груди, живота, таза, конечностей и позвоночника.</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>Переформулирование</t>
         </is>
       </c>
-    </row>
-    <row r="53" ht="36" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>4.14</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.</t>
-        </is>
-      </c>
-      <c r="C53" s="11" t="inlineStr">
-        <is>
-          <t>Отработка наложения окклюзионной (герметизирующей) повязки при ранении грудной клетки.</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>Перенесено</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения повязок на рану при выпадении органов брюшной полости, при наличии инородного предмета в ране живота, груди, спины, конечностей.</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения повязок при наличии инородного предмета в ране живота, груди, конечностей.</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>Расширение / детализация</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="36" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>4.16</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий, обездвиживание руками травмированных частей тела).</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов первой помощи при переломах. Иммобилизация (подручными средствами, аутоиммобилизация, с использованием медицинских изделий).</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>Расширение / детализация</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="inlineStr">
-        <is>
-          <t>Отработка приемов фиксации шейного отдела позвоночника.</t>
-        </is>
-      </c>
-      <c r="C56" s="11" t="inlineStr">
-        <is>
-          <t>Отработка приемов фиксации шейного отдела позвоночника.</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>Перенесено</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="36" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>4.18</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения повязок при ожогах различных областей тела. Применение местного охлаждения.</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения повязок при ожогах различных областей тела. Применение местного охлаждения.</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="36" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>4.19</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения термоизолирующей повязки при отморожениях.</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов наложения термоизолирующей повязки при отморожениях.</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="36" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов придания оптимального положения тела пострадавшему при отсутствии сознания, травмах различных областей тела, значительной кровопотере.</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов придания оптимального положения тела пострадавшему при отсутствии сознания, травмах различных областей тела, значительной кровопотере.</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="36" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>4.21</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов экстренного извлечения пострадавшего из труднодоступного места, отработка основных приемов (пострадавший в сознании, пострадавший без сознания).</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Отработка приемов экстренного извлечения пострадавшего из труднодоступного места, отработка основных приемов (пострадавший в сознании, пострадавший без сознания).</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="36" customHeight="1">
-      <c r="A61" s="9" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов перемещения пострадавших на руках одним, 2 и более участниками оказания первой помощи. Отработка приемов перемещения пострадавших с травмами головы, шеи, груди, спины, живота, таза, конечностей и позвоночника.</t>
-        </is>
-      </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов перемещения пострадавших на руках одним, двумя и более участниками оказания первой помощи. Отработка приемов переноски пострадавших с травмами головы, шеи, груди, живота, таза, конечностей и позвоночника.</t>
-        </is>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>«двумя» заменено на «2». Во второй фразе «переноски» заменено на «перемещения» (унификация термина). В перечень областей травм добавлена «спина».</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="48" customHeight="1">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов оказания психологической поддержки пострадавших при различных острых психологических реакциях на стресс. Способы самопомощи в экстремальных ситуациях.</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Отработка приемов оказания психологической поддержки пострадавшим при различных острых стрессовых реакциях. Способы самопомощи в экстремальных ситуациях.</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
         <is>
           <t>Переформулирование</t>
         </is>
       </c>
-    </row>
-    <row r="62" ht="36" customHeight="1">
-      <c r="A62" s="9" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов оказания психологической поддержки пострадавших при различных острых психологических реакциях на стресс. Способы самопомощи в экстремальных ситуациях.</t>
-        </is>
-      </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>Отработка приемов оказания психологической поддержки пострадавшим при различных острых стрессовых реакциях. Способы самопомощи в экстремальных ситуациях.</t>
-        </is>
-      </c>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>Переформулирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="36" customHeight="1">
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>«пострадавшим» → «пострадавших» (управление слова «поддержки»). «острых стрессовых реакциях» → «острых психологических реакциях на стресс». Фраза о самопомощи без изменений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1">
       <c r="A63" s="12" t="inlineStr">
         <is>
           <t>И.1</t>
@@ -4225,11 +4654,16 @@
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Исключено (нет в ред. от 30.06.2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="36" customHeight="1">
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>Как отдельный элемент программы убрано. Частично перекрыто новыми пунктами о порядке и приоритетности оказания первой помощи (п. 1.3) и перечнем состояний/мероприятий (п. 1.4), но само понятие больше не формулируется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="48" customHeight="1">
       <c r="A64" s="12" t="inlineStr">
         <is>
           <t>И.2</t>
@@ -4247,11 +4681,16 @@
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Исключено (нет в ред. от 30.06.2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="36" customHeight="1">
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>Весь блок об ошибках, осложнениях, показаниях к прекращению реанимации и действиях после прекращения удалён из теории. В новой теме 3 аналога нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="48" customHeight="1">
       <c r="A65" s="12" t="inlineStr">
         <is>
           <t>И.3</t>
@@ -4269,11 +4708,16 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Исключено (нет в ред. от 30.06.2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="36" customHeight="1">
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>Отдельный пункт об особенностях реанимации у детей удалён. В новой теме 3 аналога нет (в т.ч. не сохранена и детализация помощи ребёнку при инородном теле).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="48" customHeight="1">
       <c r="A66" s="12" t="inlineStr">
         <is>
           <t>И.4</t>
@@ -4291,11 +4735,16 @@
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Исключено (нет в ред. от 30.06.2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="36" customHeight="1">
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>Отдельный пункт о носовом кровотечении удалён. В новой теме 2 (кровотечения) аналога нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="48" customHeight="1">
       <c r="A67" s="12" t="inlineStr">
         <is>
           <t>И.5</t>
@@ -4313,11 +4762,16 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Исключено (нет в ред. от 30.06.2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="36" customHeight="1">
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>Тема травматического шока полностью исключена из Приложения № 2 новой редакции. Ни в теме 2, ни в теме 4 не воспроизведена.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="48" customHeight="1">
       <c r="A68" s="12" t="inlineStr">
         <is>
           <t>И.6</t>
@@ -4335,7 +4789,12 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Исключено (нет в ред. от 30.06.2026)</t>
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>Единый практический пункт заменён тремя пунктами новой темы 2 (2.7–2.9). Не сохранены: пальцевое прижатие конкретных артерий; максимальное сгибание конечности в суставе; уточнения «жгут-закрутка, ремень»; ранения таза. Сохранены в изменённом виде: прямое давление, давящая повязка, табельные/импровизированные жгуты.</t>
         </is>
       </c>
     </row>
